--- a/eval_results.xlsx
+++ b/eval_results.xlsx
@@ -420,10 +420,10 @@
         <v>render_addition</v>
       </c>
       <c r="B2" t="str">
-        <v>8872 + 6865 verify=true</v>
+        <v>274 + 8476 verify=true</v>
       </c>
       <c r="C2" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253084926.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254169439.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="3">
@@ -431,10 +431,10 @@
         <v>render_addition</v>
       </c>
       <c r="B3" t="str">
-        <v>3869 + 9288 verify=false</v>
+        <v>6403 + 5331 verify=false</v>
       </c>
       <c r="C3" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253083549.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254168976.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="4">
@@ -442,10 +442,10 @@
         <v>render_addition</v>
       </c>
       <c r="B4" t="str">
-        <v>2103 + 1495 verify=true</v>
+        <v>8023 + 5130 verify=true</v>
       </c>
       <c r="C4" t="str">
-        <v>❌ 渲染失败 [2103+1495]: Upload failed (409): {"message":"is at 699f5d2aed195c70159e55370254d92fd34b656d but expected ec5f994e7ab06c25b92f5f509aade0f51dc30a18","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254170855.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="5">
@@ -453,10 +453,10 @@
         <v>render_addition</v>
       </c>
       <c r="B5" t="str">
-        <v>935.5 + 2893.7 verify=false</v>
+        <v>5319.7 + 8276.6 verify=false</v>
       </c>
       <c r="C5" t="str">
-        <v>❌ 渲染失败 [935.5+2893.7]: Upload failed (409): {"message":"is at 24dfb870d54b126135a1a57a3cd50e6dd9cd04c6 but expected 976f3316791336f6536cc1e89501037d3ad7a3de","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254172688.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="6">
@@ -464,10 +464,10 @@
         <v>render_addition</v>
       </c>
       <c r="B6" t="str">
-        <v>1008.44 + 8240.09 verify=true</v>
+        <v>9118.22 + 2442.7 verify=true</v>
       </c>
       <c r="C6" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253086042.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254172901.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="7">
@@ -475,10 +475,10 @@
         <v>render_addition</v>
       </c>
       <c r="B7" t="str">
-        <v>284 + 4343 verify=false</v>
+        <v>422 + 7645 verify=false</v>
       </c>
       <c r="C7" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253086549.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254172504.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +486,10 @@
         <v>render_addition</v>
       </c>
       <c r="B8" t="str">
-        <v>5492 + 566 verify=true</v>
+        <v>4415 + 5464 verify=true</v>
       </c>
       <c r="C8" t="str">
-        <v>❌ 渲染失败 [5492+566]: Upload failed (409): {"message":"is at e1bcd9b9a1aba54d78b9272aaf50b52b9fb240dc but expected 74c8e0130ceada5a1c8b0d90f192b53ff35403fd","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254175121.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="9">
@@ -497,10 +497,10 @@
         <v>render_addition</v>
       </c>
       <c r="B9" t="str">
-        <v>6691 + 6596 verify=false</v>
+        <v>9216 + 7519 verify=false</v>
       </c>
       <c r="C9" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253087867.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254174985.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="10">
@@ -508,10 +508,10 @@
         <v>render_addition</v>
       </c>
       <c r="B10" t="str">
-        <v>1400.5 + 3974.9 verify=true</v>
+        <v>1535.7 + 6475.7 verify=true</v>
       </c>
       <c r="C10" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253087599.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254174914.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="11">
@@ -519,10 +519,10 @@
         <v>render_addition</v>
       </c>
       <c r="B11" t="str">
-        <v>6170.26 + 4657.16 verify=false</v>
+        <v>9841.47 + 119.44 verify=false</v>
       </c>
       <c r="C11" t="str">
-        <v>❌ 渲染失败 [6170.26+4657.16]: Upload failed (409): {"message":"is at a2f60d5d727340a4074e9d548ebccb80e2f91f91 but expected 00cb1a0b6131d7bf5e6a8d2d5c71255c4889f8c2","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254178960.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="12">
@@ -530,10 +530,10 @@
         <v>render_addition</v>
       </c>
       <c r="B12" t="str">
-        <v>2893 + 5801 verify=true</v>
+        <v>3841 + 6566 verify=true</v>
       </c>
       <c r="C12" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253089087.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254179098.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="13">
@@ -541,10 +541,10 @@
         <v>render_addition</v>
       </c>
       <c r="B13" t="str">
-        <v>176 + 6540 verify=false</v>
+        <v>419 + 8193 verify=false</v>
       </c>
       <c r="C13" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253088817.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254179170.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="14">
@@ -552,10 +552,10 @@
         <v>render_addition</v>
       </c>
       <c r="B14" t="str">
-        <v>2151 + 7512 verify=true</v>
+        <v>7159 + 5220 verify=true</v>
       </c>
       <c r="C14" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253090924.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254183281.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="15">
@@ -563,10 +563,10 @@
         <v>render_addition</v>
       </c>
       <c r="B15" t="str">
-        <v>3273.2 + 822.3 verify=false</v>
+        <v>6954.6 + 9895.2 verify=false</v>
       </c>
       <c r="C15" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253090621.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254183393.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="16">
@@ -574,10 +574,10 @@
         <v>render_addition</v>
       </c>
       <c r="B16" t="str">
-        <v>9419.08 + 1671.8 verify=true</v>
+        <v>3385.13 + 8872.83 verify=true</v>
       </c>
       <c r="C16" t="str">
-        <v>❌ 渲染失败 [9419.08+1671.8]: Upload failed (409): {"message":"is at f57c48b88b2635b4c0b47e9cfb89c0e6acca3664 but expected e17e8fc12684153d94dea4d7bcc78bf62c06ae68","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254183778.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="17">
@@ -585,10 +585,10 @@
         <v>render_addition</v>
       </c>
       <c r="B17" t="str">
-        <v>9279 + 3174 verify=false</v>
+        <v>6049 + 1484 verify=false</v>
       </c>
       <c r="C17" t="str">
-        <v>❌ 渲染失败 [9279+3174]: Upload failed (409): {"message":"is at bb1c78de2fdbdb57dea875bf8e03186589baa35d but expected 1dbcad646f1fa79a7a9202f4b6942b213c2098e2","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254186404.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="18">
@@ -596,10 +596,10 @@
         <v>render_addition</v>
       </c>
       <c r="B18" t="str">
-        <v>1197 + 1282 verify=true</v>
+        <v>2384 + 2042 verify=true</v>
       </c>
       <c r="C18" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253091997.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254186333.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="19">
@@ -607,10 +607,10 @@
         <v>render_addition</v>
       </c>
       <c r="B19" t="str">
-        <v>1797 + 8152 verify=false</v>
+        <v>8119 + 467 verify=false</v>
       </c>
       <c r="C19" t="str">
-        <v>❌ 渲染失败 [1797+8152]: Upload failed (409): {"message":"is at bb1c78de2fdbdb57dea875bf8e03186589baa35d but expected 1dbcad646f1fa79a7a9202f4b6942b213c2098e2","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254186093.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="20">
@@ -618,10 +618,10 @@
         <v>render_addition</v>
       </c>
       <c r="B20" t="str">
-        <v>732.9 + 1532.7 verify=true</v>
+        <v>6432.9 + 7422.8 verify=true</v>
       </c>
       <c r="C20" t="str">
-        <v>❌ 渲染失败 [732.9+1532.7]: Upload failed (409): {"message":"is at 03a0f2cc0c775088fd456ac40b9ceabdc0c8319b but expected bb1c78de2fdbdb57dea875bf8e03186589baa35d","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254189048.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="21">
@@ -629,10 +629,10 @@
         <v>render_addition</v>
       </c>
       <c r="B21" t="str">
-        <v>2619 + 9129.84 verify=false</v>
+        <v>9812 + 556.09 verify=false</v>
       </c>
       <c r="C21" t="str">
-        <v>❌ 渲染失败 [2619+9129.84]: Upload failed (409): {"message":"is at 03a0f2cc0c775088fd456ac40b9ceabdc0c8319b but expected bb1c78de2fdbdb57dea875bf8e03186589baa35d","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254189158.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="22">
@@ -640,10 +640,10 @@
         <v>render_addition</v>
       </c>
       <c r="B22" t="str">
-        <v>8555 + 169 verify=true</v>
+        <v>5356 + 8930 verify=true</v>
       </c>
       <c r="C22" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253093517.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254189303.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         <v>render_addition</v>
       </c>
       <c r="B23" t="str">
-        <v>2609 + 811 verify=false</v>
+        <v>5009 + 1637 verify=false</v>
       </c>
       <c r="C23" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253095265.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254191843.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="24">
@@ -662,10 +662,10 @@
         <v>render_addition</v>
       </c>
       <c r="B24" t="str">
-        <v>7938 + 848 verify=true</v>
+        <v>5220 + 1413 verify=true</v>
       </c>
       <c r="C24" t="str">
-        <v>❌ 渲染失败 [7938+848]: Upload failed (409): {"message":"is at a653f71ba45249a2b722d741de255f489c21b22c but expected 03a0f2cc0c775088fd456ac40b9ceabdc0c8319b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254191698.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="25">
@@ -673,10 +673,10 @@
         <v>render_addition</v>
       </c>
       <c r="B25" t="str">
-        <v>6750.8 + 2160.9 verify=false</v>
+        <v>1711.8 + 1713.6 verify=false</v>
       </c>
       <c r="C25" t="str">
-        <v>❌ 渲染失败 [6750.8+2160.9]: Upload failed (409): {"message":"is at a653f71ba45249a2b722d741de255f489c21b22c but expected 03a0f2cc0c775088fd456ac40b9ceabdc0c8319b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254191771.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="26">
@@ -684,10 +684,10 @@
         <v>render_addition</v>
       </c>
       <c r="B26" t="str">
-        <v>4252.12 + 102.94 verify=true</v>
+        <v>6405.66 + 1196.85 verify=true</v>
       </c>
       <c r="C26" t="str">
-        <v>❌ 渲染失败 [4252.12+102.94]: Upload failed (409): {"message":"is at 4d5b103c50d7c1aa34a5a7190e4afca7f0add68c but expected a653f71ba45249a2b722d741de255f489c21b22c","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254196069.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="27">
@@ -695,10 +695,10 @@
         <v>render_addition</v>
       </c>
       <c r="B27" t="str">
-        <v>1419 + 9615 verify=false</v>
+        <v>4436 + 7357 verify=false</v>
       </c>
       <c r="C27" t="str">
-        <v>❌ 渲染失败 [1419+9615]: Upload failed (409): {"message":"is at 4d5b103c50d7c1aa34a5a7190e4afca7f0add68c but expected a653f71ba45249a2b722d741de255f489c21b22c","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254195923.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="28">
@@ -706,10 +706,10 @@
         <v>render_addition</v>
       </c>
       <c r="B28" t="str">
-        <v>127 + 8669 verify=true</v>
+        <v>1878 + 7705 verify=true</v>
       </c>
       <c r="C28" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253096849.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254196205.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="29">
@@ -717,10 +717,10 @@
         <v>render_addition</v>
       </c>
       <c r="B29" t="str">
-        <v>4159 + 9121 verify=false</v>
+        <v>9733 + 4233 verify=false</v>
       </c>
       <c r="C29" t="str">
-        <v>❌ 渲染失败 [4159+9121]: Upload failed (409): {"message":"is at 1b872d2450446dd18c1c8016562a2482dd7d205d but expected 4d5b103c50d7c1aa34a5a7190e4afca7f0add68c","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254200118.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="30">
@@ -728,10 +728,10 @@
         <v>render_addition</v>
       </c>
       <c r="B30" t="str">
-        <v>4196.6 + 7679.3 verify=true</v>
+        <v>4312.1 + 46.1 verify=true</v>
       </c>
       <c r="C30" t="str">
-        <v>❌ 渲染失败 [4196.6+7679.3]: Upload failed (409): {"message":"is at 1b872d2450446dd18c1c8016562a2482dd7d205d but expected 4d5b103c50d7c1aa34a5a7190e4afca7f0add68c","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254200630.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="31">
@@ -739,10 +739,10 @@
         <v>render_addition</v>
       </c>
       <c r="B31" t="str">
-        <v>7771.75 + 9308.17 verify=false</v>
+        <v>5228.46 + 1189.62 verify=false</v>
       </c>
       <c r="C31" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253098696.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254200048.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="32">
@@ -750,10 +750,10 @@
         <v>render_addition</v>
       </c>
       <c r="B32" t="str">
-        <v>7833 + 5555 verify=true</v>
+        <v>9432 + 5148 verify=true</v>
       </c>
       <c r="C32" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253100619.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254203104.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="33">
@@ -761,10 +761,10 @@
         <v>render_addition</v>
       </c>
       <c r="B33" t="str">
-        <v>6967 + 2457 verify=false</v>
+        <v>8692 + 9140 verify=false</v>
       </c>
       <c r="C33" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253100242.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254202965.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="34">
@@ -772,10 +772,10 @@
         <v>render_addition</v>
       </c>
       <c r="B34" t="str">
-        <v>5618 + 253 verify=true</v>
+        <v>5224 + 4599 verify=true</v>
       </c>
       <c r="C34" t="str">
-        <v>❌ 渲染失败 [5618+253]: Upload failed (409): {"message":"is at d97648eaaec2193ebbecfc0019bbf39677063b22 but expected 1b872d2450446dd18c1c8016562a2482dd7d205d","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254202895.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="35">
@@ -783,10 +783,10 @@
         <v>render_addition</v>
       </c>
       <c r="B35" t="str">
-        <v>696.6 + 9035.7 verify=false</v>
+        <v>5489.7 + 490.3 verify=false</v>
       </c>
       <c r="C35" t="str">
-        <v>❌ 渲染失败 [696.6+9035.7]: Upload failed (409): {"message":"is at 8c4c41ff5ad7d4375bd3e2984567755ec59520e8 but expected ebe63f14396220a19bbd53f8ef02b05d2347a2ff","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254205973.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="36">
@@ -794,10 +794,10 @@
         <v>render_addition</v>
       </c>
       <c r="B36" t="str">
-        <v>5616.48 + 9398.25 verify=true</v>
+        <v>6744.84 + 6450.6 verify=true</v>
       </c>
       <c r="C36" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253101665.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254205903.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="37">
@@ -805,10 +805,10 @@
         <v>render_addition</v>
       </c>
       <c r="B37" t="str">
-        <v>4568 + 8801 verify=false</v>
+        <v>1740 + 6193 verify=false</v>
       </c>
       <c r="C37" t="str">
-        <v>❌ 渲染失败 [4568+8801]: Upload failed (409): {"message":"is at 8c4c41ff5ad7d4375bd3e2984567755ec59520e8 but expected ebe63f14396220a19bbd53f8ef02b05d2347a2ff","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254205756.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="38">
@@ -816,10 +816,10 @@
         <v>render_addition</v>
       </c>
       <c r="B38" t="str">
-        <v>1400 + 7550 verify=true</v>
+        <v>287 + 1750 verify=true</v>
       </c>
       <c r="C38" t="str">
-        <v>❌ 渲染失败 [1400+7550]: Upload failed (409): {"message":"is at cae4a334b990a6f8049a2edb152b54098680bf52 but expected 8c4c41ff5ad7d4375bd3e2984567755ec59520e8","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254211918.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="39">
@@ -827,10 +827,10 @@
         <v>render_addition</v>
       </c>
       <c r="B39" t="str">
-        <v>1694 + 6511 verify=false</v>
+        <v>8508 + 2537 verify=false</v>
       </c>
       <c r="C39" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253102838.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254211641.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="40">
@@ -838,10 +838,10 @@
         <v>render_addition</v>
       </c>
       <c r="B40" t="str">
-        <v>6070.6 + 234.6 verify=true</v>
+        <v>1058.8 + 7294.5 verify=true</v>
       </c>
       <c r="C40" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253103114.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254211781.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="41">
@@ -849,10 +849,10 @@
         <v>render_addition</v>
       </c>
       <c r="B41" t="str">
-        <v>1197.87 + 5024.08 verify=false</v>
+        <v>7462.95 + 4355.65 verify=false</v>
       </c>
       <c r="C41" t="str">
-        <v>❌ 渲染失败 [1197.87+5024.08]: Upload failed (409): {"message":"is at 4783f8f009a72519c56dabe2b655a516d235571d but expected 0f0a546caa4b051c9ad4e3b934eafe64a68fc746","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254214042.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="42">
@@ -860,10 +860,10 @@
         <v>render_addition</v>
       </c>
       <c r="B42" t="str">
-        <v>1280 + 4088 verify=true</v>
+        <v>9606 + 8042 verify=true</v>
       </c>
       <c r="C42" t="str">
-        <v>❌ 渲染失败 [1280+4088]: Upload failed (409): {"message":"is at 4783f8f009a72519c56dabe2b655a516d235571d but expected 0f0a546caa4b051c9ad4e3b934eafe64a68fc746","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254214189.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="43">
@@ -871,10 +871,10 @@
         <v>render_addition</v>
       </c>
       <c r="B43" t="str">
-        <v>5497 + 8005 verify=false</v>
+        <v>2825 + 744 verify=false</v>
       </c>
       <c r="C43" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253105479.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254214551.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="44">
@@ -882,10 +882,10 @@
         <v>render_addition</v>
       </c>
       <c r="B44" t="str">
-        <v>1328 + 2014 verify=true</v>
+        <v>976 + 6221 verify=true</v>
       </c>
       <c r="C44" t="str">
-        <v>❌ 渲染失败 [1328+2014]: Upload failed (409): {"message":"is at a1190a6d2cab654f59a727910158d610710c97cd but expected 4783f8f009a72519c56dabe2b655a516d235571d","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254217313.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="45">
@@ -893,10 +893,10 @@
         <v>render_addition</v>
       </c>
       <c r="B45" t="str">
-        <v>3598.6 + 833.1 verify=false</v>
+        <v>8749.7 + 3762.7 verify=false</v>
       </c>
       <c r="C45" t="str">
-        <v>❌ 渲染失败 [3598.6+833.1]: Upload failed (409): {"message":"is at a1190a6d2cab654f59a727910158d610710c97cd but expected 4783f8f009a72519c56dabe2b655a516d235571d","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254217555.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="46">
@@ -904,10 +904,10 @@
         <v>render_addition</v>
       </c>
       <c r="B46" t="str">
-        <v>2705.49 + 8079.14 verify=true</v>
+        <v>9319.2 + 8361.45 verify=true</v>
       </c>
       <c r="C46" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253107228.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254217484.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="47">
@@ -915,10 +915,10 @@
         <v>render_addition</v>
       </c>
       <c r="B47" t="str">
-        <v>3415 + 8392 verify=false</v>
+        <v>9970 + 6712 verify=false</v>
       </c>
       <c r="C47" t="str">
-        <v>❌ 渲染失败 [3415+8392]: Upload failed (409): {"message":"is at 42ed9ea693b7e8d0d0b7e099d7056e178accab69 but expected a1190a6d2cab654f59a727910158d610710c97cd","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254219936.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="48">
@@ -926,10 +926,10 @@
         <v>render_addition</v>
       </c>
       <c r="B48" t="str">
-        <v>6978 + 160 verify=true</v>
+        <v>1814 + 6839 verify=true</v>
       </c>
       <c r="C48" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253109046.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254220075.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="49">
@@ -937,10 +937,10 @@
         <v>render_addition</v>
       </c>
       <c r="B49" t="str">
-        <v>2736 + 1816 verify=false</v>
+        <v>8859 + 9267 verify=false</v>
       </c>
       <c r="C49" t="str">
-        <v>❌ 渲染失败 [2736+1816]: Upload failed (409): {"message":"is at 42ed9ea693b7e8d0d0b7e099d7056e178accab69 but expected a1190a6d2cab654f59a727910158d610710c97cd","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254219867.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="50">
@@ -948,10 +948,10 @@
         <v>render_addition</v>
       </c>
       <c r="B50" t="str">
-        <v>746.4 + 1074.6 verify=true</v>
+        <v>6577.8 + 934.3 verify=true</v>
       </c>
       <c r="C50" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253110237.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254224789.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="51">
@@ -959,10 +959,10 @@
         <v>render_addition</v>
       </c>
       <c r="B51" t="str">
-        <v>5550.37 + 6318.63 verify=false</v>
+        <v>7274.57 + 484.02 verify=false</v>
       </c>
       <c r="C51" t="str">
-        <v>❌ 渲染失败 [5550.37+6318.63]: Upload failed (409): {"message":"is at 801d6212d595a49af64438c6f5977e21df896239 but expected 42ed9ea693b7e8d0d0b7e099d7056e178accab69","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254224859.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="52">
@@ -970,10 +970,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B52" t="str">
-        <v>7377 - 1350 verify=true</v>
+        <v>6747 - 6024 verify=true</v>
       </c>
       <c r="C52" t="str">
-        <v>❌ 渲染失败 [7377-1350]: Upload failed (409): {"message":"is at 801d6212d595a49af64438c6f5977e21df896239 but expected 42ed9ea693b7e8d0d0b7e099d7056e178accab69","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254224650.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="53">
@@ -981,10 +981,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B53" t="str">
-        <v>2509 - 356 verify=false</v>
+        <v>8161 - 6137 verify=false</v>
       </c>
       <c r="C53" t="str">
-        <v>❌ 渲染失败 [2509-356]: Upload failed (409): {"message":"is at dd15bb733edb511b520f27254bbfdcdc95d2e586 but expected 801d6212d595a49af64438c6f5977e21df896239","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254229644.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="54">
@@ -992,10 +992,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B54" t="str">
-        <v>977.6 - 746.9 verify=true</v>
+        <v>7619.8 - 192.3 verify=true</v>
       </c>
       <c r="C54" t="str">
-        <v>❌ 渲染失败 [977.6-746.9]: Upload failed (409): {"message":"is at dd15bb733edb511b520f27254bbfdcdc95d2e586 but expected 801d6212d595a49af64438c6f5977e21df896239","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254229950.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="55">
@@ -1003,10 +1003,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B55" t="str">
-        <v>8738.86 - 6692.21 verify=false</v>
+        <v>6353.54 - 1531.46 verify=false</v>
       </c>
       <c r="C55" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253111571.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254229801.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="56">
@@ -1014,10 +1014,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B56" t="str">
-        <v>9394 - 4848 verify=true</v>
+        <v>1500 - 396 verify=true</v>
       </c>
       <c r="C56" t="str">
-        <v>❌ 渲染失败 [9394-4848]: Upload failed (409): {"message":"is at e0d25912a2e5d13f2327501639110385d88c69c7 but expected dd15bb733edb511b520f27254bbfdcdc95d2e586","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254232280.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="57">
@@ -1025,10 +1025,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B57" t="str">
-        <v>2677 - 1213 verify=false</v>
+        <v>9275 - 272 verify=false</v>
       </c>
       <c r="C57" t="str">
-        <v>❌ 渲染失败 [2677-1213]: Upload failed (409): {"message":"is at e0d25912a2e5d13f2327501639110385d88c69c7 but expected dd15bb733edb511b520f27254bbfdcdc95d2e586","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254232393.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="58">
@@ -1036,10 +1036,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B58" t="str">
-        <v>8424.4 - 7172.9 verify=true</v>
+        <v>571.2 - 193.8 verify=true</v>
       </c>
       <c r="C58" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253112853.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254232532.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="59">
@@ -1047,10 +1047,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B59" t="str">
-        <v>1638.36 - 876.11 verify=false</v>
+        <v>7488.7 - 5026.42 verify=false</v>
       </c>
       <c r="C59" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253114364.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254234500.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="60">
@@ -1058,10 +1058,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B60" t="str">
-        <v>5126 - 1595 verify=true</v>
+        <v>5572 - 1402 verify=true</v>
       </c>
       <c r="C60" t="str">
-        <v>❌ 渲染失败 [5126-1595]: Upload failed (409): {"message":"is at 6a47f3d007354568023df1fefb681b52601cb753 but expected e0d25912a2e5d13f2327501639110385d88c69c7","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254234639.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="61">
@@ -1069,10 +1069,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B61" t="str">
-        <v>5022 - 576 verify=false</v>
+        <v>8300 - 3832 verify=false</v>
       </c>
       <c r="C61" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253114149.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254234709.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="62">
@@ -1080,10 +1080,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B62" t="str">
-        <v>6430.3 - 2563.3 verify=true</v>
+        <v>4645.4 - 3875.1 verify=true</v>
       </c>
       <c r="C62" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253116424.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254238982.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="63">
@@ -1091,10 +1091,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B63" t="str">
-        <v>6169.62 - 5972.63 verify=false</v>
+        <v>6316.42 - 772.1 verify=false</v>
       </c>
       <c r="C63" t="str">
-        <v>❌ 渲染失败 [6169.62-5972.63]: Upload failed (409): {"message":"is at 73ea66ba038532bc1d5b2607d04446ec3eb11de5 but expected 05b9963eb2233997abac6d5d62044834642f75f6","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254238733.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="64">
@@ -1102,10 +1102,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B64" t="str">
-        <v>2857 - 1919 verify=true</v>
+        <v>3276 - 2640 verify=true</v>
       </c>
       <c r="C64" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253116194.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254239124.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="65">
@@ -1113,10 +1113,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B65" t="str">
-        <v>9491 - 4478 verify=false</v>
+        <v>8348 - 7015 verify=false</v>
       </c>
       <c r="C65" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253118685.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254242435.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="66">
@@ -1124,10 +1124,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B66" t="str">
-        <v>3421.5 - 3334.8 verify=true</v>
+        <v>866.8 - 529 verify=true</v>
       </c>
       <c r="C66" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253119231.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254242130.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="67">
@@ -1135,10 +1135,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B67" t="str">
-        <v>7462.56 - 5567.91 verify=false</v>
+        <v>901.56 - 610.4 verify=false</v>
       </c>
       <c r="C67" t="str">
-        <v>❌ 渲染失败 [7462.56-5567.91]: Upload failed (409): {"message":"is at 8bd53ce689b4441ba0c1872f79ae180491a69298 but expected 08c017a3ae44ae3e25fe7afcb367363428543ea7","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254241884.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="68">
@@ -1146,10 +1146,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B68" t="str">
-        <v>7884 - 1484 verify=true</v>
+        <v>9888 - 9300 verify=true</v>
       </c>
       <c r="C68" t="str">
-        <v>❌ 渲染失败 [7884-1484]: Upload failed (409): {"message":"is at 40942f3039b38ffeb6086c9575e5e54e525185a9 but expected 0bb7bfe8a2a60211b2c581218c609879601d6ef2","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254244510.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="69">
@@ -1157,10 +1157,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B69" t="str">
-        <v>2042 - 1497 verify=false</v>
+        <v>2882 - 1386 verify=false</v>
       </c>
       <c r="C69" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253121112.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254244789.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="70">
@@ -1168,10 +1168,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B70" t="str">
-        <v>6505.9 - 3002.2 verify=true</v>
+        <v>4330.1 - 1768.8 verify=true</v>
       </c>
       <c r="C70" t="str">
-        <v>❌ 渲染失败 [6505.9-3002.2]: Upload failed (409): {"message":"is at 40942f3039b38ffeb6086c9575e5e54e525185a9 but expected 0bb7bfe8a2a60211b2c581218c609879601d6ef2","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254244344.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="71">
@@ -1179,10 +1179,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B71" t="str">
-        <v>9195.15 - 2238.55 verify=false</v>
+        <v>6656.97 - 1011.14 verify=false</v>
       </c>
       <c r="C71" t="str">
-        <v>❌ 渲染失败 [9195.15-2238.55]: Upload failed (409): {"message":"is at 3934e6e38c811ff53e2c9986a63822604375d025 but expected 40942f3039b38ffeb6086c9575e5e54e525185a9","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254246964.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="72">
@@ -1190,10 +1190,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B72" t="str">
-        <v>3944 - 1867 verify=true</v>
+        <v>1465 - 325 verify=true</v>
       </c>
       <c r="C72" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253122869.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254246891.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="73">
@@ -1201,10 +1201,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B73" t="str">
-        <v>5543 - 2057 verify=false</v>
+        <v>5405 - 2048 verify=false</v>
       </c>
       <c r="C73" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253122624.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254246750.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="74">
@@ -1212,10 +1212,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B74" t="str">
-        <v>5134 - 893 verify=true</v>
+        <v>6401.8 - 4220.7 verify=true</v>
       </c>
       <c r="C74" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253124264.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254251670.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="75">
@@ -1223,10 +1223,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B75" t="str">
-        <v>6064.36 - 2830.77 verify=false</v>
+        <v>5817.42 - 1726.6 verify=false</v>
       </c>
       <c r="C75" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253123984.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254251741.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="76">
@@ -1234,10 +1234,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B76" t="str">
-        <v>6329 - 2756 verify=true</v>
+        <v>6142 - 416 verify=true</v>
       </c>
       <c r="C76" t="str">
-        <v>❌ 渲染失败 [6329-2756]: Upload failed (409): {"message":"is at 63c1264c354a5d5936b8c40824ba40363e7bf324 but expected 7f7b10993291c8974851e078e3fcfff4a0fb65d2","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254251500.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="77">
@@ -1245,10 +1245,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B77" t="str">
-        <v>1076 - 399 verify=false</v>
+        <v>4424 - 3147 verify=false</v>
       </c>
       <c r="C77" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253125210.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254253913.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="78">
@@ -1256,10 +1256,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B78" t="str">
-        <v>5697 - 2769.6 verify=true</v>
+        <v>291.7 - 67.8 verify=true</v>
       </c>
       <c r="C78" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253125425.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254254050.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="79">
@@ -1267,10 +1267,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B79" t="str">
-        <v>3842.75 - 2081.97 verify=false</v>
+        <v>8308.71 - 4586.35 verify=false</v>
       </c>
       <c r="C79" t="str">
-        <v>❌ 渲染失败 [3842.75-2081.97]: Upload failed (409): {"message":"is at 8c28bc9950fd68810d2000149edf32b6c5de1348 but expected e5bd5029e8b2f653d544ccb81d6d23b4f9ade368","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254254139.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="80">
@@ -1278,10 +1278,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B80" t="str">
-        <v>5042 - 6 verify=true</v>
+        <v>9252 - 5513 verify=true</v>
       </c>
       <c r="C80" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253129003.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254256322.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="81">
@@ -1289,10 +1289,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B81" t="str">
-        <v>9102 - 7401 verify=false</v>
+        <v>4886 - 144 verify=false</v>
       </c>
       <c r="C81" t="str">
-        <v>❌ 渲染失败 [9102-7401]: Upload failed (409): {"message":"is at dd7c6039d1196fe62a717eb7c2c4321ceca87680 but expected 0f0d43ea3c710a59109f2ed975fc83c6f243cf0f","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254256530.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="82">
@@ -1300,10 +1300,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B82" t="str">
-        <v>6772.1 - 4523.3 verify=true</v>
+        <v>5619.3 - 5245.7 verify=true</v>
       </c>
       <c r="C82" t="str">
-        <v>❌ 渲染失败 [6772.1-4523.3]: Upload failed (409): {"message":"is at dd7c6039d1196fe62a717eb7c2c4321ceca87680 but expected 0f0d43ea3c710a59109f2ed975fc83c6f243cf0f","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254256461.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="83">
@@ -1311,10 +1311,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B83" t="str">
-        <v>9562.8 - 4334.3 verify=false</v>
+        <v>7913.31 - 4354.42 verify=false</v>
       </c>
       <c r="C83" t="str">
-        <v>❌ 渲染失败 [9562.8-4334.3]: Upload failed (409): {"message":"is at cd04be547ceec7e1c937a5bb6eec46bdd8075965 but expected dd7c6039d1196fe62a717eb7c2c4321ceca87680","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254260735.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="84">
@@ -1322,10 +1322,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B84" t="str">
-        <v>8843 - 3759 verify=true</v>
+        <v>7535 - 4877 verify=true</v>
       </c>
       <c r="C84" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253130268.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254260595.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="85">
@@ -1333,10 +1333,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B85" t="str">
-        <v>1695 - 717 verify=false</v>
+        <v>6703 - 4811 verify=false</v>
       </c>
       <c r="C85" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253130022.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254260664.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="86">
@@ -1344,10 +1344,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B86" t="str">
-        <v>493 - 484.9 verify=true</v>
+        <v>2840.8 - 2227.5 verify=true</v>
       </c>
       <c r="C86" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253131353.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254265178.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="87">
@@ -1355,10 +1355,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B87" t="str">
-        <v>8502.44 - 1328.06 verify=false</v>
+        <v>5615.66 - 419.03 verify=false</v>
       </c>
       <c r="C87" t="str">
-        <v>❌ 渲染失败 [8502.44-1328.06]: Upload failed (409): {"message":"is at 192c905d96bbc442be34af32a835f45acf1ff42a but expected 3629eac46fe5091edaa9af88428b85512015fb39","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254265033.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="88">
@@ -1366,10 +1366,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B88" t="str">
-        <v>8788 - 918 verify=true</v>
+        <v>1803 - 1695 verify=true</v>
       </c>
       <c r="C88" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253131502.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254265317.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="89">
@@ -1377,10 +1377,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B89" t="str">
-        <v>1225 - 602 verify=false</v>
+        <v>9400 - 6885 verify=false</v>
       </c>
       <c r="C89" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253132804.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254268440.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="90">
@@ -1388,10 +1388,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B90" t="str">
-        <v>2302.7 - 1333.1 verify=true</v>
+        <v>5929.9 - 4116 verify=true</v>
       </c>
       <c r="C90" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253133369.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254268211.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="91">
@@ -1399,10 +1399,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B91" t="str">
-        <v>2799.68 - 2479.74 verify=false</v>
+        <v>5610.71 - 2910.64 verify=false</v>
       </c>
       <c r="C91" t="str">
-        <v>❌ 渲染失败 [2799.68-2479.74]: Upload failed (409): {"message":"is at 2162b3b678dc2d5482e59917f1f6193b9d0d0e6c but expected 192c905d96bbc442be34af32a835f45acf1ff42a","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254267962.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="92">
@@ -1410,10 +1410,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B92" t="str">
-        <v>2124 - 369 verify=true</v>
+        <v>8014 - 5076 verify=true</v>
       </c>
       <c r="C92" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253134477.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254270711.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="93">
@@ -1421,10 +1421,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B93" t="str">
-        <v>3373 - 1849 verify=false</v>
+        <v>9931 - 5017 verify=false</v>
       </c>
       <c r="C93" t="str">
-        <v>❌ 渲染失败 [3373-1849]: Upload failed (409): {"message":"is at 71a8286c8273de3c707de7705928d42620e9ca5b but expected ed74da029f13ddb7dbf86ef99d5851ac1dcb8685","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254270576.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="94">
@@ -1432,10 +1432,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B94" t="str">
-        <v>2702.2 - 1505 verify=true</v>
+        <v>225.1 - 70.2 verify=true</v>
       </c>
       <c r="C94" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253134826.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254270506.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="95">
@@ -1443,10 +1443,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B95" t="str">
-        <v>3413.36 - 525.73 verify=false</v>
+        <v>333.75 - 188.17 verify=false</v>
       </c>
       <c r="C95" t="str">
-        <v>❌ 渲染失败 [3413.36-525.73]: Upload failed (409): {"message":"is at 80882943ac19a7df214f8828b1544d284ad15849 but expected cc1fe712e39cd00a380752764b0aec4b39fc8384","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254274887.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="96">
@@ -1454,10 +1454,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B96" t="str">
-        <v>3073 - 481 verify=true</v>
+        <v>9775 - 1882 verify=true</v>
       </c>
       <c r="C96" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253136177.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254274700.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="97">
@@ -1465,10 +1465,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B97" t="str">
-        <v>8523 - 6599 verify=false</v>
+        <v>2442 - 730 verify=false</v>
       </c>
       <c r="C97" t="str">
-        <v>❌ 渲染失败 [8523-6599]: Upload failed (409): {"message":"is at 80882943ac19a7df214f8828b1544d284ad15849 but expected cc1fe712e39cd00a380752764b0aec4b39fc8384","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254274818.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="98">
@@ -1476,10 +1476,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B98" t="str">
-        <v>7372.1 - 332.8 verify=true</v>
+        <v>2166.1 - 485.7 verify=true</v>
       </c>
       <c r="C98" t="str">
-        <v>❌ 渲染失败 [7372.1-332.8]: Upload failed (409): {"message":"is at 2cbfe18388b9dc740ca95a19e830c64f5912f813 but expected 80882943ac19a7df214f8828b1544d284ad15849","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254279071.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="99">
@@ -1487,10 +1487,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B99" t="str">
-        <v>8212.17 - 1052.14 verify=false</v>
+        <v>6983.28 - 5.11 verify=false</v>
       </c>
       <c r="C99" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253137399.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254278930.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="100">
@@ -1498,10 +1498,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B100" t="str">
-        <v>7291 - 5513 verify=true</v>
+        <v>1823 - 953 verify=true</v>
       </c>
       <c r="C100" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253137831.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254279212.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="101">
@@ -1509,10 +1509,10 @@
         <v>render_subtraction</v>
       </c>
       <c r="B101" t="str">
-        <v>3538 - 1802 verify=false</v>
+        <v>9312 - 738 verify=false</v>
       </c>
       <c r="C101" t="str">
-        <v>❌ 渲染失败 [3538-1802]: Upload failed (409): {"message":"is at 2e895ca9a7aa3ed2ccbe8f1a5ee9cac488f0b50c but expected 89168f0327e6c2ad2ff0241dd815cf5fd8208493","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254283697.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="102">
@@ -1520,10 +1520,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B102" t="str">
-        <v>860 × 97 verify=true</v>
+        <v>336 × 94 verify=true</v>
       </c>
       <c r="C102" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253139469.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254283940.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="103">
@@ -1531,10 +1531,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B103" t="str">
-        <v>889 × 89 verify=false</v>
+        <v>149 × 12 verify=false</v>
       </c>
       <c r="C103" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253139257.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254284011.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="104">
@@ -1542,10 +1542,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B104" t="str">
-        <v>385.2 × 70.7 verify=true</v>
+        <v>249.7 × 45.5 verify=true</v>
       </c>
       <c r="C104" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253141263.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254286692.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="105">
@@ -1553,10 +1553,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B105" t="str">
-        <v>882.4 × 50.79 verify=false</v>
+        <v>492.46 × 59.47 verify=false</v>
       </c>
       <c r="C105" t="str">
-        <v>❌ 渲染失败 [882.4×50.79]: Upload failed (409): {"message":"is at c5eac1d2e3f1a983fba7eb07b701aec40dae37e1 but expected ee85e557a1d06c4ebed0878f553544b17e5307e5","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254286767.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="106">
@@ -1564,10 +1564,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B106" t="str">
-        <v>300 × 80 verify=true</v>
+        <v>196 × 45 verify=true</v>
       </c>
       <c r="C106" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253140980.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254286526.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="107">
@@ -1575,10 +1575,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B107" t="str">
-        <v>488 × 89 verify=false</v>
+        <v>403 × 37 verify=false</v>
       </c>
       <c r="C107" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253143573.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254291212.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="108">
@@ -1586,10 +1586,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B108" t="str">
-        <v>667.8 × 12.3 verify=true</v>
+        <v>528.2 × 33.6 verify=true</v>
       </c>
       <c r="C108" t="str">
-        <v>❌ 渲染失败 [667.8×12.3]: Upload failed (409): {"message":"is at a50a212b8add5bb471651635437fb513ad4c52d1 but expected 8633adf600f0a8d756124cfeb009dec03d884dde","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254291031.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="109">
@@ -1597,10 +1597,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B109" t="str">
-        <v>9.44 × 92.57 verify=false</v>
+        <v>620.03 × 5.26 verify=false</v>
       </c>
       <c r="C109" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253143046.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254291141.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="110">
@@ -1608,10 +1608,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B110" t="str">
-        <v>497 × 22 verify=true</v>
+        <v>399 × 16 verify=true</v>
       </c>
       <c r="C110" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253145104.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254296019.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="111">
@@ -1619,10 +1619,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B111" t="str">
-        <v>35 × 26 verify=false</v>
+        <v>172 × 61 verify=false</v>
       </c>
       <c r="C111" t="str">
-        <v>❌ 渲染失败 [35×26]: Upload failed (409): {"message":"is at 743496e318810ec996c6834be611656bb51cfe70 but expected a50a212b8add5bb471651635437fb513ad4c52d1","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254295723.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="112">
@@ -1630,10 +1630,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B112" t="str">
-        <v>788.5 × 47.6 verify=true</v>
+        <v>602.5 × 14 verify=true</v>
       </c>
       <c r="C112" t="str">
-        <v>❌ 渲染失败 [788.5×47.6]: Upload failed (409): {"message":"is at 743496e318810ec996c6834be611656bb51cfe70 but expected a50a212b8add5bb471651635437fb513ad4c52d1","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254295872.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="113">
@@ -1641,10 +1641,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B113" t="str">
-        <v>558.88 × 95.08 verify=false</v>
+        <v>420.63 × 12.47 verify=false</v>
       </c>
       <c r="C113" t="str">
-        <v>❌ 渲染失败 [558.88×95.08]: Upload failed (409): {"message":"is at e2b392e672b57b88f419241b100b51c2c0bc61d8 but expected 743496e318810ec996c6834be611656bb51cfe70","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254299123.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="114">
@@ -1652,10 +1652,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B114" t="str">
-        <v>838 × 94 verify=true</v>
+        <v>866 × 11 verify=true</v>
       </c>
       <c r="C114" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253146868.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254299262.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="115">
@@ -1663,10 +1663,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B115" t="str">
-        <v>575 × 16 verify=false</v>
+        <v>337 × 27 verify=false</v>
       </c>
       <c r="C115" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253146559.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254298958.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="116">
@@ -1674,10 +1674,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B116" t="str">
-        <v>80.5 × 83.1 verify=true</v>
+        <v>957.2 × 83.2 verify=true</v>
       </c>
       <c r="C116" t="str">
-        <v>❌ 渲染失败 [80.5×83.1]: Upload failed (409): {"message":"is at 7dbb6a157d0d55bcbd59f5a6e850624f471c69e3 but expected 062542c26218fe7205fd9ac77931834fdb36ae8c","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254301390.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="117">
@@ -1685,10 +1685,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B117" t="str">
-        <v>147.04 × 49.62 verify=false</v>
+        <v>246.58 × 94.92 verify=false</v>
       </c>
       <c r="C117" t="str">
-        <v>❌ 渲染失败 [147.04×49.62]: Upload failed (409): {"message":"is at 7dbb6a157d0d55bcbd59f5a6e850624f471c69e3 but expected 062542c26218fe7205fd9ac77931834fdb36ae8c","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254301609.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="118">
@@ -1696,10 +1696,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B118" t="str">
-        <v>787 × 75 verify=true</v>
+        <v>819 × 61 verify=true</v>
       </c>
       <c r="C118" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253148128.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254301537.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="119">
@@ -1707,10 +1707,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B119" t="str">
-        <v>408 × 84 verify=false</v>
+        <v>28 × 56 verify=false</v>
       </c>
       <c r="C119" t="str">
-        <v>❌ 渲染失败 [408×84]: Upload failed (409): {"message":"is at 88ea0020b807aa2ce3b219d0d98661edb86e8c71 but expected 7dbb6a157d0d55bcbd59f5a6e850624f471c69e3","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254305645.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="120">
@@ -1718,10 +1718,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B120" t="str">
-        <v>841.2 × 16.1 verify=true</v>
+        <v>671.3 × 75 verify=true</v>
       </c>
       <c r="C120" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253149627.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254305791.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="121">
@@ -1729,10 +1729,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B121" t="str">
-        <v>697.86 × 53.89 verify=false</v>
+        <v>950.3 × 86.91 verify=false</v>
       </c>
       <c r="C121" t="str">
-        <v>❌ 渲染失败 [697.86×53.89]: Upload failed (409): {"message":"is at 88ea0020b807aa2ce3b219d0d98661edb86e8c71 but expected 7dbb6a157d0d55bcbd59f5a6e850624f471c69e3","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254305862.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="122">
@@ -1740,10 +1740,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B122" t="str">
-        <v>241 × 61 verify=true</v>
+        <v>906 × 40 verify=true</v>
       </c>
       <c r="C122" t="str">
-        <v>❌ 渲染失败 [241×61]: Upload failed (409): {"message":"is at 02e003fa9f1f24d333b70ff582889ac9acfd3bb0 but expected 88ea0020b807aa2ce3b219d0d98661edb86e8c71","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254310076.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="123">
@@ -1751,10 +1751,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B123" t="str">
-        <v>579 × 95 verify=false</v>
+        <v>61 × 19 verify=false</v>
       </c>
       <c r="C123" t="str">
-        <v>❌ 渲染失败 [579×95]: Upload failed (409): {"message":"is at 02e003fa9f1f24d333b70ff582889ac9acfd3bb0 but expected 88ea0020b807aa2ce3b219d0d98661edb86e8c71","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254310149.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="124">
@@ -1762,10 +1762,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B124" t="str">
-        <v>614.2 × 83.3 verify=true</v>
+        <v>917.5 × 59.9 verify=true</v>
       </c>
       <c r="C124" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253151138.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254310295.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="125">
@@ -1773,10 +1773,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B125" t="str">
-        <v>959.33 × 60.76 verify=false</v>
+        <v>634.79 × 70.36 verify=false</v>
       </c>
       <c r="C125" t="str">
-        <v>❌ 渲染失败 [959.33×60.76]: Upload failed (409): {"message":"is at 55e612c6fe2242e3efc1751de6572b934a0d394f but expected 02e003fa9f1f24d333b70ff582889ac9acfd3bb0","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254313124.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="126">
@@ -1784,10 +1784,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B126" t="str">
-        <v>809 × 79 verify=true</v>
+        <v>919 × 93 verify=true</v>
       </c>
       <c r="C126" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253152750.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254313047.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="127">
@@ -1795,10 +1795,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B127" t="str">
-        <v>911 × 50 verify=false</v>
+        <v>241 × 61 verify=false</v>
       </c>
       <c r="C127" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253152528.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254312903.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="128">
@@ -1806,10 +1806,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B128" t="str">
-        <v>722.6 × 95.4 verify=true</v>
+        <v>115.4 × 95.5 verify=true</v>
       </c>
       <c r="C128" t="str">
-        <v>❌ 渲染失败 [722.6×95.4]: Upload failed (409): {"message":"is at c8498a22bb148b064b21820118a044191e193c93 but expected 9d1ab66e952e074b7a936b209f4ca15f0352b20e","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254315743.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="129">
@@ -1817,10 +1817,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B129" t="str">
-        <v>825.43 × 2.26 verify=false</v>
+        <v>478.41 × 65.51 verify=false</v>
       </c>
       <c r="C129" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253154252.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254315600.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="130">
@@ -1828,10 +1828,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B130" t="str">
-        <v>742 × 84 verify=true</v>
+        <v>57 × 37 verify=true</v>
       </c>
       <c r="C130" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253154560.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254315525.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="131">
@@ -1839,10 +1839,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B131" t="str">
-        <v>408 × 52 verify=false</v>
+        <v>990 × 46 verify=false</v>
       </c>
       <c r="C131" t="str">
-        <v>❌ 渲染失败 [408×52]: Upload failed (409): {"message":"is at 51e9d33b926a6fe4749f8f4c50a38ce477b8632a but expected 0312aa50aa7b200351103387d809d2a50d5756e1","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254318438.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="132">
@@ -1850,10 +1850,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B132" t="str">
-        <v>430.8 × 81.4 verify=true</v>
+        <v>137.1 × 46.4 verify=true</v>
       </c>
       <c r="C132" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253155788.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254318680.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="133">
@@ -1861,10 +1861,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B133" t="str">
-        <v>942.09 × 7.58 verify=false</v>
+        <v>430.84 × 57.96 verify=false</v>
       </c>
       <c r="C133" t="str">
-        <v>❌ 渲染失败 [942.09×7.58]: Upload failed (409): {"message":"is at 51e9d33b926a6fe4749f8f4c50a38ce477b8632a but expected 0312aa50aa7b200351103387d809d2a50d5756e1","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254318192.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="134">
@@ -1872,10 +1872,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B134" t="str">
-        <v>223 × 59 verify=true</v>
+        <v>514 × 95 verify=true</v>
       </c>
       <c r="C134" t="str">
-        <v>❌ 渲染失败 [223×59]: Upload failed (409): {"message":"is at 250b564f0c7575f5c5061fe34206fc0fdcbe2a40 but expected 51e9d33b926a6fe4749f8f4c50a38ce477b8632a","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254321350.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="135">
@@ -1883,10 +1883,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B135" t="str">
-        <v>62 × 18 verify=false</v>
+        <v>643 × 85 verify=false</v>
       </c>
       <c r="C135" t="str">
-        <v>❌ 渲染失败 [62×18]: Upload failed (409): {"message":"is at 250b564f0c7575f5c5061fe34206fc0fdcbe2a40 but expected 51e9d33b926a6fe4749f8f4c50a38ce477b8632a","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254321205.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="136">
@@ -1894,10 +1894,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B136" t="str">
-        <v>624.9 × 9.4 verify=true</v>
+        <v>751 × 71.4 verify=true</v>
       </c>
       <c r="C136" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253157379.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254321084.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="137">
@@ -1905,10 +1905,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B137" t="str">
-        <v>7.48 × 98.87 verify=false</v>
+        <v>930.39 × 8.23 verify=false</v>
       </c>
       <c r="C137" t="str">
-        <v>❌ 渲染失败 [7.48×98.87]: Upload failed (409): {"message":"is at 18b9025fa42bb2475b2943cf53ca02c4eff03c90 but expected 250b564f0c7575f5c5061fe34206fc0fdcbe2a40","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254325555.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="138">
@@ -1916,10 +1916,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B138" t="str">
-        <v>385 × 5 verify=true</v>
+        <v>233 × 34 verify=true</v>
       </c>
       <c r="C138" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253158962.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254325485.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="139">
@@ -1927,10 +1927,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B139" t="str">
-        <v>142 × 91 verify=false</v>
+        <v>845 × 57 verify=false</v>
       </c>
       <c r="C139" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253158693.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254325342.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="140">
@@ -1938,10 +1938,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B140" t="str">
-        <v>741.6 × 70.1 verify=true</v>
+        <v>185.6 × 67.2 verify=true</v>
       </c>
       <c r="C140" t="str">
-        <v>❌ 渲染失败 [741.6×70.1]: Upload failed (409): {"message":"is at a5dba7a961fc4f670ced729d2910f40592dbd2ab but expected 78860e8178c34c122bd9c6fa6fc476d8df542ac7","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254330128.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="141">
@@ -1949,10 +1949,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B141" t="str">
-        <v>740.74 × 20.23 verify=false</v>
+        <v>826.4 × 80.95 verify=false</v>
       </c>
       <c r="C141" t="str">
-        <v>❌ 渲染失败 [740.74×20.23]: Upload failed (409): {"message":"is at a5dba7a961fc4f670ced729d2910f40592dbd2ab but expected 78860e8178c34c122bd9c6fa6fc476d8df542ac7","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254330201.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="142">
@@ -1960,10 +1960,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B142" t="str">
-        <v>358 × 59 verify=true</v>
+        <v>39 × 84 verify=true</v>
       </c>
       <c r="C142" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253160041.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254330465.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="143">
@@ -1971,10 +1971,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B143" t="str">
-        <v>169 × 82 verify=false</v>
+        <v>689 × 19 verify=false</v>
       </c>
       <c r="C143" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253161473.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254332539.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="144">
@@ -1982,10 +1982,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B144" t="str">
-        <v>13.4 × 79 verify=true</v>
+        <v>883.9 × 8 verify=true</v>
       </c>
       <c r="C144" t="str">
-        <v>❌ 渲染失败 [13.4×79]: Upload failed (409): {"message":"is at 1b9f1c30235fd969aee1ef226f9de8c9107d97bd but expected a8e1475a1e6fc3fec8687fd43b94c784ba779404","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254332721.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="145">
@@ -1993,10 +1993,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B145" t="str">
-        <v>97.71 × 88.25 verify=false</v>
+        <v>465.1 × 83.28 verify=false</v>
       </c>
       <c r="C145" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253161807.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254332468.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="146">
@@ -2004,10 +2004,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B146" t="str">
-        <v>964 × 26 verify=true</v>
+        <v>362 × 49 verify=true</v>
       </c>
       <c r="C146" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253163435.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254334811.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="147">
@@ -2015,10 +2015,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B147" t="str">
-        <v>242 × 51 verify=false</v>
+        <v>7 × 74 verify=false</v>
       </c>
       <c r="C147" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253163022.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254335052.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="148">
@@ -2026,10 +2026,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B148" t="str">
-        <v>433.7 × 64.6 verify=true</v>
+        <v>162.6 × 24.2 verify=true</v>
       </c>
       <c r="C148" t="str">
-        <v>❌ 渲染失败 [433.7×64.6]: Upload failed (409): {"message":"is at 7e124e3f33c4941b4a78148d82eacfb5a14efc99 but expected 1b9f1c30235fd969aee1ef226f9de8c9107d97bd","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254334979.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="149">
@@ -2037,10 +2037,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B149" t="str">
-        <v>578.6 × 26.59 verify=false</v>
+        <v>515.17 × 40.06 verify=false</v>
       </c>
       <c r="C149" t="str">
-        <v>❌ 渲染失败 [578.6×26.59]: Upload failed (409): {"message":"is at b78e48d9dc0f62d5a044cdd4868379d8ef9e3135 but expected 0d366b50117da859792b0fdd9b542d850b61d8d7","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254338815.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="150">
@@ -2048,10 +2048,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B150" t="str">
-        <v>222 × 34 verify=true</v>
+        <v>575 × 60 verify=true</v>
       </c>
       <c r="C150" t="str">
-        <v>❌ 渲染失败 [222×34]: Upload failed (409): {"message":"is at b78e48d9dc0f62d5a044cdd4868379d8ef9e3135 but expected 0d366b50117da859792b0fdd9b542d850b61d8d7","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254338714.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="151">
@@ -2059,10 +2059,10 @@
         <v>render_multiplication</v>
       </c>
       <c r="B151" t="str">
-        <v>408 × 80 verify=false</v>
+        <v>443 × 39 verify=false</v>
       </c>
       <c r="C151" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253164691.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254338888.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="152">
@@ -2070,10 +2070,10 @@
         <v>render_division</v>
       </c>
       <c r="B152" t="str">
-        <v>118 ÷ 74 verify=true</v>
+        <v>533 ÷ 22 verify=true</v>
       </c>
       <c r="C152" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253166884.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254343240.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="153">
@@ -2081,10 +2081,10 @@
         <v>render_division</v>
       </c>
       <c r="B153" t="str">
-        <v>833 ÷ 26 verify=false</v>
+        <v>575 ÷ 5 verify=false</v>
       </c>
       <c r="C153" t="str">
-        <v>❌ 渲染失败 [833÷26]: Upload failed (409): {"message":"is at 19252a44172a93255f5a311e073056b377454631 but expected b78e48d9dc0f62d5a044cdd4868379d8ef9e3135","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254342799.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="154">
@@ -2092,10 +2092,10 @@
         <v>render_division</v>
       </c>
       <c r="B154" t="str">
-        <v>704.6 ÷ 74.4 verify=true</v>
+        <v>717.6 ÷ 49.9 verify=true</v>
       </c>
       <c r="C154" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253167116.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254343092.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="155">
@@ -2103,10 +2103,10 @@
         <v>render_division</v>
       </c>
       <c r="B155" t="str">
-        <v>596 ÷ 43 verify=false</v>
+        <v>954 ÷ 42 verify=false</v>
       </c>
       <c r="C155" t="str">
-        <v>❌ 渲染失败 [596÷43]: Upload failed (409): {"message":"is at 3a8374e84f4943549496aab2f4d13b7812f16a1c but expected 10874bc0c3bf1f770f31072ae836767165fe8418","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254345681.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="156">
@@ -2114,10 +2114,10 @@
         <v>render_division</v>
       </c>
       <c r="B156" t="str">
-        <v>303 ÷ 95 verify=true</v>
+        <v>356 ÷ 47 verify=true</v>
       </c>
       <c r="C156" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253168643.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254345955.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="157">
@@ -2125,10 +2125,10 @@
         <v>render_division</v>
       </c>
       <c r="B157" t="str">
-        <v>874.5 ÷ 30.3 verify=false</v>
+        <v>866.6 ÷ 46.8 verify=false</v>
       </c>
       <c r="C157" t="str">
-        <v>❌ 渲染失败 [874.5÷30.3]: Upload failed (409): {"message":"is at 3a8374e84f4943549496aab2f4d13b7812f16a1c but expected 10874bc0c3bf1f770f31072ae836767165fe8418","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254345759.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="158">
@@ -2136,10 +2136,10 @@
         <v>render_division</v>
       </c>
       <c r="B158" t="str">
-        <v>589 ÷ 72 verify=true</v>
+        <v>829 ÷ 32 verify=true</v>
       </c>
       <c r="C158" t="str">
-        <v>❌ 渲染失败 [589÷72]: Upload failed (409): {"message":"is at 114cf767e39f5a91aee10450f9540622dc9ca5ed but expected 3a8374e84f4943549496aab2f4d13b7812f16a1c","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254348115.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="159">
@@ -2147,10 +2147,10 @@
         <v>render_division</v>
       </c>
       <c r="B159" t="str">
-        <v>236 ÷ 49 verify=false</v>
+        <v>255 ÷ 31 verify=false</v>
       </c>
       <c r="C159" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253170655.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254347968.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="160">
@@ -2158,10 +2158,10 @@
         <v>render_division</v>
       </c>
       <c r="B160" t="str">
-        <v>314.2 ÷ 91.8 verify=true</v>
+        <v>384.2 ÷ 38.2 verify=true</v>
       </c>
       <c r="C160" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253170399.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254348319.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="161">
@@ -2169,10 +2169,10 @@
         <v>render_division</v>
       </c>
       <c r="B161" t="str">
-        <v>997 ÷ 98 verify=false</v>
+        <v>419 ÷ 92 verify=false</v>
       </c>
       <c r="C161" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253176760.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254350462.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="162">
@@ -2180,10 +2180,10 @@
         <v>render_division</v>
       </c>
       <c r="B162" t="str">
-        <v>211 ÷ 53 verify=true</v>
+        <v>216 ÷ 79 verify=true</v>
       </c>
       <c r="C162" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253176432.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254350616.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="163">
@@ -2191,10 +2191,10 @@
         <v>render_division</v>
       </c>
       <c r="B163" t="str">
-        <v>984.1 ÷ 15.4 verify=false</v>
+        <v>442.6 ÷ 5.8 verify=false</v>
       </c>
       <c r="C163" t="str">
-        <v>❌ 渲染失败 [984.1÷15.4]: Upload failed (409): {"message":"is at 4d0541725200df8b5d97979892a99a3efa50e3e5 but expected cd3b4d4c80e5c7bef28400ac7c2fe145198bed03","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254350716.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="164">
@@ -2202,10 +2202,10 @@
         <v>render_division</v>
       </c>
       <c r="B164" t="str">
-        <v>862 ÷ 57 verify=true</v>
+        <v>795 ÷ 85 verify=true</v>
       </c>
       <c r="C164" t="str">
-        <v>❌ 渲染失败 [862÷57]: Upload failed (409): {"message":"is at b30a6d909fb162131a15014cb967ca888a401f80 but expected 849dac75af906002968b2221c1bd8bf51d8b405b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254353509.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="165">
@@ -2213,10 +2213,10 @@
         <v>render_division</v>
       </c>
       <c r="B165" t="str">
-        <v>752 ÷ 38 verify=false</v>
+        <v>475 ÷ 56 verify=false</v>
       </c>
       <c r="C165" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253178322.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254353605.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="166">
@@ -2224,10 +2224,10 @@
         <v>render_division</v>
       </c>
       <c r="B166" t="str">
-        <v>462.1 ÷ 94.2 verify=true</v>
+        <v>693.1 ÷ 17.6 verify=true</v>
       </c>
       <c r="C166" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253178595.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254353751.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="167">
@@ -2235,10 +2235,10 @@
         <v>render_division</v>
       </c>
       <c r="B167" t="str">
-        <v>700 ÷ 58 verify=false</v>
+        <v>717 ÷ 93 verify=false</v>
       </c>
       <c r="C167" t="str">
-        <v>❌ 渲染失败 [700÷58]: Upload failed (409): {"message":"is at 7406ee802620a74e78840fb26d3fb48c2edccd39 but expected b30a6d909fb162131a15014cb967ca888a401f80","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254358275.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="168">
@@ -2246,10 +2246,10 @@
         <v>render_division</v>
       </c>
       <c r="B168" t="str">
-        <v>693 ÷ 37 verify=true</v>
+        <v>948 ÷ 35 verify=true</v>
       </c>
       <c r="C168" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253179883.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254358023.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="169">
@@ -2257,10 +2257,10 @@
         <v>render_division</v>
       </c>
       <c r="B169" t="str">
-        <v>753.9 ÷ 84.1 verify=false</v>
+        <v>825.1 ÷ 89.9 verify=false</v>
       </c>
       <c r="C169" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253180120.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254358188.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="170">
@@ -2268,10 +2268,10 @@
         <v>render_division</v>
       </c>
       <c r="B170" t="str">
-        <v>818 ÷ 87 verify=true</v>
+        <v>976 ÷ 5 verify=true</v>
       </c>
       <c r="C170" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253182121.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254363336.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="171">
@@ -2279,10 +2279,10 @@
         <v>render_division</v>
       </c>
       <c r="B171" t="str">
-        <v>199 ÷ 10 verify=false</v>
+        <v>517 ÷ 96 verify=false</v>
       </c>
       <c r="C171" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253181712.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254362996.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="172">
@@ -2290,10 +2290,10 @@
         <v>render_division</v>
       </c>
       <c r="B172" t="str">
-        <v>300 ÷ 55.1 verify=true</v>
+        <v>823.9 ÷ 49.8 verify=true</v>
       </c>
       <c r="C172" t="str">
-        <v>❌ 渲染失败 [300÷55.1]: Upload failed (409): {"message":"is at bc53b30637cd0c952e96c1a78df64a8436f54af5 but expected d41df7892b16f422f869cc8be18c2bdee7fd001a","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254363187.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="173">
@@ -2301,10 +2301,10 @@
         <v>render_division</v>
       </c>
       <c r="B173" t="str">
-        <v>347 ÷ 2 verify=false</v>
+        <v>962 ÷ 33 verify=false</v>
       </c>
       <c r="C173" t="str">
-        <v>❌ 渲染失败 [347÷2]: Upload failed (409): {"message":"is at 741d3e6d011dd689fc5a77079259f8acdc7bda99 but expected eb30b86f77930e7a959ec11a297ca45f46a1c6a0","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254366025.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="174">
@@ -2312,10 +2312,10 @@
         <v>render_division</v>
       </c>
       <c r="B174" t="str">
-        <v>188 ÷ 13 verify=true</v>
+        <v>382 ÷ 64 verify=true</v>
       </c>
       <c r="C174" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253183546.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254366182.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="175">
@@ -2323,10 +2323,10 @@
         <v>render_division</v>
       </c>
       <c r="B175" t="str">
-        <v>952.4 ÷ 37.8 verify=false</v>
+        <v>325 ÷ 75.6 verify=false</v>
       </c>
       <c r="C175" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253183213.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254365945.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="176">
@@ -2334,10 +2334,10 @@
         <v>render_division</v>
       </c>
       <c r="B176" t="str">
-        <v>554 ÷ 18 verify=true</v>
+        <v>928 ÷ 96 verify=true</v>
       </c>
       <c r="C176" t="str">
-        <v>❌ 渲染失败 [554÷18]: Upload failed (409): {"message":"is at cc077cc2dde67f5272fb76824d46912e4ab650e5 but expected d83b9fd70014a508d7d36c02b28c6d7d2c26e8aa","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254370836.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="177">
@@ -2345,10 +2345,10 @@
         <v>render_division</v>
       </c>
       <c r="B177" t="str">
-        <v>708 ÷ 66 verify=false</v>
+        <v>255 ÷ 66 verify=false</v>
       </c>
       <c r="C177" t="str">
-        <v>❌ 渲染失败 [708÷66]: Upload failed (409): {"message":"is at cc077cc2dde67f5272fb76824d46912e4ab650e5 but expected d83b9fd70014a508d7d36c02b28c6d7d2c26e8aa","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254370929.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="178">
@@ -2356,10 +2356,10 @@
         <v>render_division</v>
       </c>
       <c r="B178" t="str">
-        <v>295.4 ÷ 66.1 verify=true</v>
+        <v>508.6 ÷ 67.9 verify=true</v>
       </c>
       <c r="C178" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253185006.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254371156.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="179">
@@ -2367,10 +2367,10 @@
         <v>render_division</v>
       </c>
       <c r="B179" t="str">
-        <v>724 ÷ 85 verify=false</v>
+        <v>453 ÷ 69 verify=false</v>
       </c>
       <c r="C179" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253187560.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254373387.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="180">
@@ -2378,10 +2378,10 @@
         <v>render_division</v>
       </c>
       <c r="B180" t="str">
-        <v>418 ÷ 87 verify=true</v>
+        <v>792 ÷ 83 verify=true</v>
       </c>
       <c r="C180" t="str">
-        <v>❌ 渲染失败 [418÷87]: Upload failed (409): {"message":"is at 5467870582491f5afa9e667a78e3d67c8dfa4ec8 but expected cc077cc2dde67f5272fb76824d46912e4ab650e5","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254373567.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="181">
@@ -2389,10 +2389,10 @@
         <v>render_division</v>
       </c>
       <c r="B181" t="str">
-        <v>767.8 ÷ 44.8 verify=false</v>
+        <v>464.9 ÷ 95.5 verify=false</v>
       </c>
       <c r="C181" t="str">
-        <v>❌ 渲染失败 [767.8÷44.8]: Upload failed (409): {"message":"is at 5467870582491f5afa9e667a78e3d67c8dfa4ec8 but expected cc077cc2dde67f5272fb76824d46912e4ab650e5","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254373259.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="182">
@@ -2400,10 +2400,10 @@
         <v>render_division</v>
       </c>
       <c r="B182" t="str">
-        <v>489 ÷ 65 verify=true</v>
+        <v>882 ÷ 22 verify=true</v>
       </c>
       <c r="C182" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253188915.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254376302.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="183">
@@ -2411,10 +2411,10 @@
         <v>render_division</v>
       </c>
       <c r="B183" t="str">
-        <v>484 ÷ 30 verify=false</v>
+        <v>875 ÷ 58 verify=false</v>
       </c>
       <c r="C183" t="str">
-        <v>❌ 渲染失败 [484÷30]: Upload failed (409): {"message":"is at bda020593c58fe584a9ee2ce31d09af27e167dd4 but expected 5467870582491f5afa9e667a78e3d67c8dfa4ec8","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254376153.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="184">
@@ -2422,10 +2422,10 @@
         <v>render_division</v>
       </c>
       <c r="B184" t="str">
-        <v>75.5 ÷ 24.1 verify=true</v>
+        <v>130.4 ÷ 79.4 verify=true</v>
       </c>
       <c r="C184" t="str">
-        <v>❌ 渲染失败 [75.5÷24.1]: Upload failed (409): {"message":"is at bda020593c58fe584a9ee2ce31d09af27e167dd4 but expected 5467870582491f5afa9e667a78e3d67c8dfa4ec8","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254376031.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="185">
@@ -2433,10 +2433,10 @@
         <v>render_division</v>
       </c>
       <c r="B185" t="str">
-        <v>871 ÷ 88 verify=false</v>
+        <v>306 ÷ 76 verify=false</v>
       </c>
       <c r="C185" t="str">
-        <v>❌ 渲染失败 [871÷88]: Upload failed (409): {"message":"is at d8d01d7f993cab6ceee29881bd0da587ed3d9836 but expected bda020593c58fe584a9ee2ce31d09af27e167dd4","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254380503.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="186">
@@ -2444,10 +2444,10 @@
         <v>render_division</v>
       </c>
       <c r="B186" t="str">
-        <v>863 ÷ 30 verify=true</v>
+        <v>305 ÷ 76 verify=true</v>
       </c>
       <c r="C186" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253191259.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254380415.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="187">
@@ -2455,10 +2455,10 @@
         <v>render_division</v>
       </c>
       <c r="B187" t="str">
-        <v>891.8 ÷ 98.1 verify=false</v>
+        <v>433.8 ÷ 96.6 verify=false</v>
       </c>
       <c r="C187" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253190721.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254380643.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="188">
@@ -2466,10 +2466,10 @@
         <v>render_division</v>
       </c>
       <c r="B188" t="str">
-        <v>800 ÷ 81 verify=true</v>
+        <v>709 ÷ 92 verify=true</v>
       </c>
       <c r="C188" t="str">
-        <v>❌ 渲染失败 [800÷81]: Upload failed (409): {"message":"is at 20f4e8dfaa7201693df57a526f1845bd2aef200d but expected d8b10eaef5fff73fa0ccf8f2b40ef50acca6239b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254383325.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="189">
@@ -2477,10 +2477,10 @@
         <v>render_division</v>
       </c>
       <c r="B189" t="str">
-        <v>720 ÷ 23 verify=false</v>
+        <v>425 ÷ 87 verify=false</v>
       </c>
       <c r="C189" t="str">
-        <v>❌ 渲染失败 [720÷23]: Upload failed (409): {"message":"is at 20f4e8dfaa7201693df57a526f1845bd2aef200d but expected d8b10eaef5fff73fa0ccf8f2b40ef50acca6239b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254382975.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="190">
@@ -2488,10 +2488,10 @@
         <v>render_division</v>
       </c>
       <c r="B190" t="str">
-        <v>863.5 ÷ 89.7 verify=true</v>
+        <v>821.2 ÷ 69.3 verify=true</v>
       </c>
       <c r="C190" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253192423.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254383157.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="191">
@@ -2499,10 +2499,10 @@
         <v>render_division</v>
       </c>
       <c r="B191" t="str">
-        <v>883 ÷ 88 verify=false</v>
+        <v>417 ÷ 82 verify=false</v>
       </c>
       <c r="C191" t="str">
-        <v>❌ 渲染失败 [883÷88]: Upload failed (409): {"message":"is at 0b49fed4832053759bb26b36fd0117bc8d6cf2b5 but expected 20f4e8dfaa7201693df57a526f1845bd2aef200d","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254387573.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="192">
@@ -2510,10 +2510,10 @@
         <v>render_division</v>
       </c>
       <c r="B192" t="str">
-        <v>692 ÷ 79 verify=true</v>
+        <v>453 ÷ 29 verify=true</v>
       </c>
       <c r="C192" t="str">
-        <v>❌ 渲染失败 [692÷79]: Upload failed (409): {"message":"is at 0b49fed4832053759bb26b36fd0117bc8d6cf2b5 but expected 20f4e8dfaa7201693df57a526f1845bd2aef200d","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254387931.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="193">
@@ -2521,10 +2521,10 @@
         <v>render_division</v>
       </c>
       <c r="B193" t="str">
-        <v>955.5 ÷ 14.6 verify=false</v>
+        <v>924.8 ÷ 89.8 verify=false</v>
       </c>
       <c r="C193" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253193600.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254387762.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="194">
@@ -2532,10 +2532,10 @@
         <v>render_division</v>
       </c>
       <c r="B194" t="str">
-        <v>835 ÷ 64 verify=true</v>
+        <v>754 ÷ 12 verify=true</v>
       </c>
       <c r="C194" t="str">
-        <v>❌ 渲染失败 [835÷64]: Upload failed (409): {"message":"is at 168f1b143e2ef55cd684ccc38195cf225e19915c but expected 0b49fed4832053759bb26b36fd0117bc8d6cf2b5","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254409270.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="195">
@@ -2543,10 +2543,10 @@
         <v>render_division</v>
       </c>
       <c r="B195" t="str">
-        <v>125 ÷ 26 verify=false</v>
+        <v>743 ÷ 51 verify=false</v>
       </c>
       <c r="C195" t="str">
-        <v>❌ 渲染失败 [125÷26]: Upload failed (409): {"message":"is at 168f1b143e2ef55cd684ccc38195cf225e19915c but expected 0b49fed4832053759bb26b36fd0117bc8d6cf2b5","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254414965.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="196">
@@ -2554,10 +2554,10 @@
         <v>render_division</v>
       </c>
       <c r="B196" t="str">
-        <v>588.7 ÷ 73.4 verify=true</v>
+        <v>117.5 ÷ 39.5 verify=true</v>
       </c>
       <c r="C196" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253195341.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254409779.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="197">
@@ -2565,10 +2565,10 @@
         <v>render_division</v>
       </c>
       <c r="B197" t="str">
-        <v>736 ÷ 38 verify=false</v>
+        <v>494 ÷ 54 verify=false</v>
       </c>
       <c r="C197" t="str">
-        <v>❌ 渲染失败 [736÷38]: Upload failed (409): {"message":"is at ef8f461c63f015fafca092df6cfe44e0a49f8be7 but expected 168f1b143e2ef55cd684ccc38195cf225e19915c","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254421413.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="198">
@@ -2576,10 +2576,10 @@
         <v>render_division</v>
       </c>
       <c r="B198" t="str">
-        <v>711 ÷ 68 verify=true</v>
+        <v>846 ÷ 50 verify=true</v>
       </c>
       <c r="C198" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253197132.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254422207.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="199">
@@ -2587,10 +2587,10 @@
         <v>render_division</v>
       </c>
       <c r="B199" t="str">
-        <v>394.6 ÷ 74.9 verify=false</v>
+        <v>939.1 ÷ 94.1 verify=false</v>
       </c>
       <c r="C199" t="str">
-        <v>❌ 渲染失败 [394.6÷74.9]: Upload failed (409): {"message":"is at ef8f461c63f015fafca092df6cfe44e0a49f8be7 but expected 168f1b143e2ef55cd684ccc38195cf225e19915c","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254422691.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="200">
@@ -2598,10 +2598,10 @@
         <v>render_division</v>
       </c>
       <c r="B200" t="str">
-        <v>985 ÷ 57 verify=true</v>
+        <v>292 ÷ 6 verify=true</v>
       </c>
       <c r="C200" t="str">
-        <v>❌ 渲染失败 [985÷57]: Upload failed (409): {"message":"is at 60f668688d6a18821a6b110904079856457fb5d4 but expected ef8f461c63f015fafca092df6cfe44e0a49f8be7","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254424024.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="201">
@@ -2609,10 +2609,10 @@
         <v>render_division</v>
       </c>
       <c r="B201" t="str">
-        <v>252 ÷ 49 verify=false</v>
+        <v>178 ÷ 7 verify=false</v>
       </c>
       <c r="C201" t="str">
-        <v>❌ 渲染失败 [252÷49]: Upload failed (409): {"message":"is at 60f668688d6a18821a6b110904079856457fb5d4 but expected ef8f461c63f015fafca092df6cfe44e0a49f8be7","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254424331.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="202">
@@ -2620,10 +2620,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B202" t="str">
-        <v>7262 ÷ 26 (整除) verify=true</v>
+        <v>8528 ÷ 83 (整除) verify=true</v>
       </c>
       <c r="C202" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253198441.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254424246.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="203">
@@ -2631,10 +2631,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B203" t="str">
-        <v>7050 ÷ 70 (整除) verify=false</v>
+        <v>9434 ÷ 67 (整除) verify=false</v>
       </c>
       <c r="C203" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253199946.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254426783.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="204">
@@ -2642,10 +2642,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B204" t="str">
-        <v>5446 ÷ 79 (整除) verify=true</v>
+        <v>7137 ÷ 85 (整除) verify=true</v>
       </c>
       <c r="C204" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253200158.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254427012.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="205">
@@ -2653,10 +2653,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B205" t="str">
-        <v>555 ÷ 74 (整除) verify=false</v>
+        <v>7958 ÷ 6 (整除) verify=false</v>
       </c>
       <c r="C205" t="str">
-        <v>❌ 渲染失败 [555÷74(整除)]: Upload failed (409): {"message":"is at 2d672e0721af66507ef719333ab4c558638d678d but expected 7606ebeb2f4142ec7d20e20b41aaeec0e8fcbfe7","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254426702.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="206">
@@ -2664,10 +2664,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B206" t="str">
-        <v>5251 ÷ 46 (整除) verify=true</v>
+        <v>1737 ÷ 54 (整除) verify=true</v>
       </c>
       <c r="C206" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253202347.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254430284.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="207">
@@ -2675,10 +2675,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B207" t="str">
-        <v>3457 ÷ 44 (整除) verify=false</v>
+        <v>7103 ÷ 11 (整除) verify=false</v>
       </c>
       <c r="C207" t="str">
-        <v>❌ 渲染失败 [3457÷44(整除)]: Upload failed (409): {"message":"is at 1301e9de510fc193c07d4cf626870817d387574f but expected 2d672e0721af66507ef719333ab4c558638d678d","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254430768.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="208">
@@ -2686,10 +2686,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B208" t="str">
-        <v>4295 ÷ 49 (整除) verify=true</v>
+        <v>2160 ÷ 65 (整除) verify=true</v>
       </c>
       <c r="C208" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253201994.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254430653.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="209">
@@ -2697,10 +2697,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B209" t="str">
-        <v>6759 ÷ 57 (整除) verify=false</v>
+        <v>7616 ÷ 23 (整除) verify=false</v>
       </c>
       <c r="C209" t="str">
-        <v>❌ 渲染失败 [6759÷57(整除)]: Upload failed (409): {"message":"is at 14293ae3ba8ebe7d3a815c2a433173dc1b8b16fc but expected 6feb0d1d4411ef5f475d6fa781ff42c9c7f5124b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254435433.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="210">
@@ -2708,10 +2708,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B210" t="str">
-        <v>6725 ÷ 70 (整除) verify=true</v>
+        <v>3007 ÷ 75 (整除) verify=true</v>
       </c>
       <c r="C210" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253205123.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254435721.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="211">
@@ -2719,10 +2719,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B211" t="str">
-        <v>5359 ÷ 35 (整除) verify=false</v>
+        <v>659 ÷ 66 (整除) verify=false</v>
       </c>
       <c r="C211" t="str">
-        <v>❌ 渲染失败 [5359÷35(整除)]: Upload failed (409): {"message":"is at 14293ae3ba8ebe7d3a815c2a433173dc1b8b16fc but expected 6feb0d1d4411ef5f475d6fa781ff42c9c7f5124b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254435826.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="212">
@@ -2730,10 +2730,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B212" t="str">
-        <v>1822 ÷ 94 (整除) verify=true</v>
+        <v>4691 ÷ 84 (整除) verify=true</v>
       </c>
       <c r="C212" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253206518.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254439314.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="213">
@@ -2741,10 +2741,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B213" t="str">
-        <v>9174 ÷ 71 (整除) verify=false</v>
+        <v>4534 ÷ 79 (整除) verify=false</v>
       </c>
       <c r="C213" t="str">
-        <v>❌ 渲染失败 [9174÷71(整除)]: Upload failed (409): {"message":"is at af771bcd39b1b6e1462be7f87c3517510e254450 but expected 14293ae3ba8ebe7d3a815c2a433173dc1b8b16fc","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254439002.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="214">
@@ -2752,10 +2752,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B214" t="str">
-        <v>6256 ÷ 8 (整除) verify=true</v>
+        <v>8909 ÷ 76 (整除) verify=true</v>
       </c>
       <c r="C214" t="str">
-        <v>❌ 渲染失败 [6256÷8(整除)]: Upload failed (409): {"message":"is at af771bcd39b1b6e1462be7f87c3517510e254450 but expected 14293ae3ba8ebe7d3a815c2a433173dc1b8b16fc","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254438900.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="215">
@@ -2763,10 +2763,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B215" t="str">
-        <v>3904 ÷ 86 (整除) verify=false</v>
+        <v>8490 ÷ 18 (整除) verify=false</v>
       </c>
       <c r="C215" t="str">
-        <v>❌ 渲染失败 [3904÷86(整除)]: Upload failed (409): {"message":"is at af3ccf6a6c1b5714b38f07c0d5c88216520114e9 but expected af771bcd39b1b6e1462be7f87c3517510e254450","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254442129.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="216">
@@ -2774,10 +2774,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B216" t="str">
-        <v>2283 ÷ 21 (整除) verify=true</v>
+        <v>8360 ÷ 77 (整除) verify=true</v>
       </c>
       <c r="C216" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253208544.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254442664.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="217">
@@ -2785,10 +2785,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B217" t="str">
-        <v>1802 ÷ 4 (整除) verify=false</v>
+        <v>8350 ÷ 97 (整除) verify=false</v>
       </c>
       <c r="C217" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253208206.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254442233.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="218">
@@ -2796,10 +2796,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B218" t="str">
-        <v>9468 ÷ 46 (整除) verify=true</v>
+        <v>453 ÷ 90 (整除) verify=true</v>
       </c>
       <c r="C218" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253210275.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254444874.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="219">
@@ -2807,10 +2807,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B219" t="str">
-        <v>4959 ÷ 51 (整除) verify=false</v>
+        <v>3971 ÷ 92 (整除) verify=false</v>
       </c>
       <c r="C219" t="str">
-        <v>❌ 渲染失败 [4959÷51(整除)]: Upload failed (409): {"message":"is at ae8414395c985b041753a35238b08691ddcbcc8b but expected fbc04f2e41e17c11f29b3b160d3bcf5d52760f82","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254445292.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="220">
@@ -2818,10 +2818,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B220" t="str">
-        <v>2035 ÷ 37 (整除) verify=true</v>
+        <v>6162 ÷ 43 (整除) verify=true</v>
       </c>
       <c r="C220" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253210038.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254445179.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="221">
@@ -2829,10 +2829,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B221" t="str">
-        <v>4301 ÷ 27 (整除) verify=false</v>
+        <v>2895 ÷ 70 (整除) verify=false</v>
       </c>
       <c r="C221" t="str">
-        <v>❌ 渲染失败 [4301÷27(整除)]: Upload failed (409): {"message":"is at 533328bd2b83c6a2bb37134c4770013d1efae1e1 but expected ae8414395c985b041753a35238b08691ddcbcc8b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254448151.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="222">
@@ -2840,10 +2840,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B222" t="str">
-        <v>8215 ÷ 77 (整除) verify=true</v>
+        <v>3738 ÷ 52 (整除) verify=true</v>
       </c>
       <c r="C222" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253211752.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254447963.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="223">
@@ -2851,10 +2851,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B223" t="str">
-        <v>2056 ÷ 37 (整除) verify=false</v>
+        <v>1792 ÷ 28 (整除) verify=false</v>
       </c>
       <c r="C223" t="str">
-        <v>❌ 渲染失败 [2056÷37(整除)]: Upload failed (409): {"message":"is at 533328bd2b83c6a2bb37134c4770013d1efae1e1 but expected ae8414395c985b041753a35238b08691ddcbcc8b","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254448071.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="224">
@@ -2862,10 +2862,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B224" t="str">
-        <v>9231 ÷ 20 (整除) verify=true</v>
+        <v>5030 ÷ 66 (整除) verify=true</v>
       </c>
       <c r="C224" t="str">
-        <v>❌ 渲染失败 [9231÷20(整除)]: Upload failed (409): {"message":"is at 88bb35439c37556594f10b084de4716a15dcadb0 but expected 533328bd2b83c6a2bb37134c4770013d1efae1e1","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254452930.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="225">
@@ -2873,10 +2873,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B225" t="str">
-        <v>3251 ÷ 73 (整除) verify=false</v>
+        <v>3783 ÷ 11 (整除) verify=false</v>
       </c>
       <c r="C225" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253213263.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254453011.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="226">
@@ -2884,10 +2884,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B226" t="str">
-        <v>6045 ÷ 14 (整除) verify=true</v>
+        <v>6494 ÷ 79 (整除) verify=true</v>
       </c>
       <c r="C226" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253213930.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254453443.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="227">
@@ -2895,10 +2895,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B227" t="str">
-        <v>2216 ÷ 80 (整除) verify=false</v>
+        <v>213 ÷ 95 (整除) verify=false</v>
       </c>
       <c r="C227" t="str">
-        <v>❌ 渲染失败 [2216÷80(整除)]: Upload failed (409): {"message":"is at 76252db92a364ce067df21d90fff89fe071da702 but expected 7db95f058741ff93290552ac04e9836fee7cca79","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254455873.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="228">
@@ -2906,10 +2906,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B228" t="str">
-        <v>9729 ÷ 24 (整除) verify=true</v>
+        <v>4725 ÷ 28 (整除) verify=true</v>
       </c>
       <c r="C228" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253216218.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254455648.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="229">
@@ -2917,10 +2917,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B229" t="str">
-        <v>4065 ÷ 77 (整除) verify=false</v>
+        <v>3478 ÷ 91 (整除) verify=false</v>
       </c>
       <c r="C229" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253215912.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254455332.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="230">
@@ -2928,10 +2928,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B230" t="str">
-        <v>8346 ÷ 76 (整除) verify=true</v>
+        <v>7073 ÷ 92 (整除) verify=true</v>
       </c>
       <c r="C230" t="str">
-        <v>❌ 渲染失败 [8346÷76(整除)]: Upload failed (409): {"message":"is at 09e5fe27d51caa81a18afb9e6d43804616da9e5d but expected 383be7f41b6763e9934800adaed3435e0e4f1d32","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254458530.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="231">
@@ -2939,10 +2939,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B231" t="str">
-        <v>4140 ÷ 85 (整除) verify=false</v>
+        <v>2457 ÷ 6 (整除) verify=false</v>
       </c>
       <c r="C231" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253217385.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254458210.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="232">
@@ -2950,10 +2950,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B232" t="str">
-        <v>4014 ÷ 81 (整除) verify=true</v>
+        <v>6445 ÷ 33 (整除) verify=true</v>
       </c>
       <c r="C232" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253217814.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254458746.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="233">
@@ -2961,10 +2961,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B233" t="str">
-        <v>3293 ÷ 39 (整除) verify=false</v>
+        <v>2383 ÷ 18 (整除) verify=false</v>
       </c>
       <c r="C233" t="str">
-        <v>❌ 渲染失败 [3293÷39(整除)]: Upload failed (409): {"message":"is at 640ceb6c91eb25833a6e97ef38640ac7e84ff661 but expected b6c143461bcc52e1f9f29559e03a65fcbaedd05a","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254461851.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="234">
@@ -2972,10 +2972,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B234" t="str">
-        <v>8656 ÷ 32 (整除) verify=true</v>
+        <v>5331 ÷ 26 (整除) verify=true</v>
       </c>
       <c r="C234" t="str">
-        <v>❌ 渲染失败 [8656÷32(整除)]: Upload failed (409): {"message":"is at 640ceb6c91eb25833a6e97ef38640ac7e84ff661 but expected b6c143461bcc52e1f9f29559e03a65fcbaedd05a","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254462096.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="235">
@@ -2983,10 +2983,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B235" t="str">
-        <v>6885 ÷ 8 (整除) verify=false</v>
+        <v>6303 ÷ 26 (整除) verify=false</v>
       </c>
       <c r="C235" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253218888.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254461776.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="236">
@@ -2994,10 +2994,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B236" t="str">
-        <v>6929 ÷ 98 (整除) verify=true</v>
+        <v>1832 ÷ 24 (整除) verify=true</v>
       </c>
       <c r="C236" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253220791.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254464847.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="237">
@@ -3005,10 +3005,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B237" t="str">
-        <v>6433 ÷ 7 (整除) verify=false</v>
+        <v>9981 ÷ 14 (整除) verify=false</v>
       </c>
       <c r="C237" t="str">
-        <v>❌ 渲染失败 [6433÷7(整除)]: Upload failed (409): {"message":"is at 4248aa20a9e29d160315cc71c55cd1d399f18348 but expected 640ceb6c91eb25833a6e97ef38640ac7e84ff661","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254464931.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="238">
@@ -3016,10 +3016,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B238" t="str">
-        <v>7856 ÷ 87 (整除) verify=true</v>
+        <v>8985 ÷ 26 (整除) verify=true</v>
       </c>
       <c r="C238" t="str">
-        <v>❌ 渲染失败 [7856÷87(整除)]: Upload failed (409): {"message":"is at 4248aa20a9e29d160315cc71c55cd1d399f18348 but expected 640ceb6c91eb25833a6e97ef38640ac7e84ff661","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254465147.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="239">
@@ -3027,10 +3027,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B239" t="str">
-        <v>8048 ÷ 45 (整除) verify=false</v>
+        <v>9957 ÷ 17 (整除) verify=false</v>
       </c>
       <c r="C239" t="str">
-        <v>❌ 渲染失败 [8048÷45(整除)]: Upload failed (409): {"message":"is at fe9e019a98d9a7f4bdb7b3e61198d6acb194f50e but expected 4248aa20a9e29d160315cc71c55cd1d399f18348","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254467445.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="240">
@@ -3038,10 +3038,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B240" t="str">
-        <v>7030 ÷ 77 (整除) verify=true</v>
+        <v>9813 ÷ 69 (整除) verify=true</v>
       </c>
       <c r="C240" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253222366.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254467765.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="241">
@@ -3049,10 +3049,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B241" t="str">
-        <v>8466 ÷ 55 (整除) verify=false</v>
+        <v>9099 ÷ 13 (整除) verify=false</v>
       </c>
       <c r="C241" t="str">
-        <v>❌ 渲染失败 [8466÷55(整除)]: Upload failed (409): {"message":"is at fe9e019a98d9a7f4bdb7b3e61198d6acb194f50e but expected 4248aa20a9e29d160315cc71c55cd1d399f18348","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254467550.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="242">
@@ -3060,10 +3060,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B242" t="str">
-        <v>9912 ÷ 57 (整除) verify=true</v>
+        <v>314 ÷ 94 (整除) verify=true</v>
       </c>
       <c r="C242" t="str">
-        <v>❌ 渲染失败 [9912÷57(整除)]: Upload failed (409): {"message":"is at adbb122fe09f3f28c76fef8ee2cfdb0ad19b122e but expected fe9e019a98d9a7f4bdb7b3e61198d6acb194f50e","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254471152.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="243">
@@ -3071,10 +3071,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B243" t="str">
-        <v>9912 ÷ 57 (整除) verify=false</v>
+        <v>7087 ÷ 75 (整除) verify=false</v>
       </c>
       <c r="C243" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253224850.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254471438.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="244">
@@ -3082,10 +3082,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B244" t="str">
-        <v>8482 ÷ 47 (整除) verify=true</v>
+        <v>9390 ÷ 66 (整除) verify=true</v>
       </c>
       <c r="C244" t="str">
-        <v>❌ 渲染失败 [8482÷47(整除)]: Upload failed (409): {"message":"is at adbb122fe09f3f28c76fef8ee2cfdb0ad19b122e but expected fe9e019a98d9a7f4bdb7b3e61198d6acb194f50e","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254471363.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="245">
@@ -3093,10 +3093,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B245" t="str">
-        <v>3461 ÷ 43 (整除) verify=false</v>
+        <v>2351 ÷ 23 (整除) verify=false</v>
       </c>
       <c r="C245" t="str">
-        <v>❌ 渲染失败 [3461÷43(整除)]: Upload failed (409): {"message":"is at aa985dcff326ebc4f6298c0123d440cfea31074d but expected adbb122fe09f3f28c76fef8ee2cfdb0ad19b122e","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254476373.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="246">
@@ -3104,10 +3104,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B246" t="str">
-        <v>6824 ÷ 50 (整除) verify=true</v>
+        <v>2732 ÷ 21 (整除) verify=true</v>
       </c>
       <c r="C246" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253227765.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254476580.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="247">
@@ -3115,10 +3115,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B247" t="str">
-        <v>7667 ÷ 31 (整除) verify=false</v>
+        <v>1392 ÷ 99 (整除) verify=false</v>
       </c>
       <c r="C247" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253227130.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254476653.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="248">
@@ -3126,10 +3126,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B248" t="str">
-        <v>6390 ÷ 88 (整除) verify=true</v>
+        <v>1601 ÷ 54 (整除) verify=true</v>
       </c>
       <c r="C248" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253229670.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254479143.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="249">
@@ -3137,10 +3137,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B249" t="str">
-        <v>7444 ÷ 99 (整除) verify=false</v>
+        <v>6687 ÷ 19 (整除) verify=false</v>
       </c>
       <c r="C249" t="str">
-        <v>❌ 渲染失败 [7444÷99(整除)]: Upload failed (409): {"message":"is at 8a812dd82ff4140fd9decb1c6864945d848e8a22 but expected dd9e146bc4c484b211c615f3c0a6f27aa80fce7e","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254479217.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="250">
@@ -3148,10 +3148,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B250" t="str">
-        <v>5438 ÷ 62 (整除) verify=true</v>
+        <v>1649 ÷ 26 (整除) verify=true</v>
       </c>
       <c r="C250" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253229106.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254478932.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="251">
@@ -3159,10 +3159,10 @@
         <v>render_integer_division</v>
       </c>
       <c r="B251" t="str">
-        <v>4988 ÷ 40 (整除) verify=false</v>
+        <v>918 ÷ 12 (整除) verify=false</v>
       </c>
       <c r="C251" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253231442.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254483617.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="252">
@@ -3170,10 +3170,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B252" t="str">
-        <v>86.3 ÷ 1.4 保留1位小数</v>
+        <v>824.2 ÷ 2.1 保留1位小数</v>
       </c>
       <c r="C252" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253231149.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254483692.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="253">
@@ -3181,10 +3181,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B253" t="str">
-        <v>4207 ÷ 38 保留2位小数</v>
+        <v>5161 ÷ 95 保留2位小数</v>
       </c>
       <c r="C253" t="str">
-        <v>❌ 渲染失败 [4207÷38(decimal)]: Upload failed (409): {"message":"is at 763d914ea490505f43997e6f6adc796b96f0acae but expected 32f61e696b5e2df09f95d0b37db733ffb5c47ec6","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254483543.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="254">
@@ -3192,10 +3192,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B254" t="str">
-        <v>6305 ÷ 93 保留3位小数</v>
+        <v>7328 ÷ 86 保留3位小数</v>
       </c>
       <c r="C254" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253232591.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254490172.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="255">
@@ -3203,10 +3203,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B255" t="str">
-        <v>3183 ÷ 61 保留4位小数</v>
+        <v>6891 ÷ 87 保留4位小数</v>
       </c>
       <c r="C255" t="str">
-        <v>❌ 渲染失败 [3183÷61(decimal)]: Upload failed (409): {"message":"is at 40c99303f35edf4dfb7336b306fbfc7df9681872 but expected 8721b2cf59a85110fd44552a8d0f8b28734adef5","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254490748.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="256">
@@ -3214,10 +3214,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B256" t="str">
-        <v>457 ÷ 53 保留1位小数</v>
+        <v>6696 ÷ 32 保留1位小数</v>
       </c>
       <c r="C256" t="str">
-        <v>❌ 渲染失败 [457÷53(decimal)]: Upload failed (409): {"message":"is at 40c99303f35edf4dfb7336b306fbfc7df9681872 but expected 8721b2cf59a85110fd44552a8d0f8b28734adef5","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254498116.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="257">
@@ -3225,10 +3225,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B257" t="str">
-        <v>927.1 ÷ 6.3 保留2位小数</v>
+        <v>7.6 ÷ 1.9 保留2位小数</v>
       </c>
       <c r="C257" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253234341.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254499462.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="258">
@@ -3236,10 +3236,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B258" t="str">
-        <v>8996 ÷ 3 保留3位小数</v>
+        <v>7816 ÷ 70 保留3位小数</v>
       </c>
       <c r="C258" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253233976.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254499822.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="259">
@@ -3247,10 +3247,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B259" t="str">
-        <v>839 ÷ 23 保留4位小数</v>
+        <v>6675 ÷ 55 保留4位小数</v>
       </c>
       <c r="C259" t="str">
-        <v>❌ 渲染失败 [839÷23(decimal)]: Upload failed (409): {"message":"is at 2c7d7c926ecfc0bdc7d0cf3caea052179d62cefa but expected 40c99303f35edf4dfb7336b306fbfc7df9681872","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254500692.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="260">
@@ -3258,10 +3258,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B260" t="str">
-        <v>4680 ÷ 57 保留1位小数</v>
+        <v>2871 ÷ 82 保留1位小数</v>
       </c>
       <c r="C260" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253235617.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254502224.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="261">
@@ -3269,10 +3269,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B261" t="str">
-        <v>8381 ÷ 43 保留2位小数</v>
+        <v>248 ÷ 80 保留2位小数</v>
       </c>
       <c r="C261" t="str">
-        <v>❌ 渲染失败 [8381÷43(decimal)]: Upload failed (409): {"message":"is at 2d14081c4ddd7d992ef97967bdb7b65f6fe945d8 but expected d96b6d8891366068c12e602a75e466c7a6f995f9","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254502329.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="262">
@@ -3280,10 +3280,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B262" t="str">
-        <v>760.4 ÷ 8.4 保留3位小数</v>
+        <v>792.1 ÷ 9.1 保留3位小数</v>
       </c>
       <c r="C262" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253235358.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254502412.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="263">
@@ -3291,10 +3291,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B263" t="str">
-        <v>7253 ÷ 96 保留4位小数</v>
+        <v>5436 ÷ 95 保留4位小数</v>
       </c>
       <c r="C263" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253237081.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254506765.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="264">
@@ -3302,10 +3302,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B264" t="str">
-        <v>1182 ÷ 27 保留1位小数</v>
+        <v>3630 ÷ 81 保留1位小数</v>
       </c>
       <c r="C264" t="str">
-        <v>❌ 渲染失败 [1182÷27(decimal)]: Upload failed (409): {"message":"is at 94525a3beda37dbe994e57fc7629c7bcd596c51a but expected 65d7e311595d74170440e3b11b577608b306f049","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254506933.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="265">
@@ -3313,10 +3313,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B265" t="str">
-        <v>2345 ÷ 19 保留2位小数</v>
+        <v>1464 ÷ 33 保留2位小数</v>
       </c>
       <c r="C265" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253236814.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254506563.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="266">
@@ -3324,10 +3324,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B266" t="str">
-        <v>9901 ÷ 10 保留3位小数</v>
+        <v>5518 ÷ 21 保留3位小数</v>
       </c>
       <c r="C266" t="str">
-        <v>❌ 渲染失败 [9901÷10(decimal)]: Upload failed (409): {"message":"is at d91ad38b905322ea8a42f54a5b11cc9eec38636f but expected 154fd3ed662c1c76f67cc3db27f6dc27908a7848","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254513124.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="267">
@@ -3335,10 +3335,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B267" t="str">
-        <v>739 ÷ 5.3 保留4位小数</v>
+        <v>162.7 ÷ 6 保留4位小数</v>
       </c>
       <c r="C267" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253238879.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254513212.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="268">
@@ -3346,10 +3346,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B268" t="str">
-        <v>1689 ÷ 56 保留1位小数</v>
+        <v>569 ÷ 83 保留1位小数</v>
       </c>
       <c r="C268" t="str">
-        <v>❌ 渲染失败 [1689÷56(decimal)]: Upload failed (409): {"message":"is at d91ad38b905322ea8a42f54a5b11cc9eec38636f but expected 154fd3ed662c1c76f67cc3db27f6dc27908a7848","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254513475.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="269">
@@ -3357,10 +3357,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B269" t="str">
-        <v>4607 ÷ 84 保留2位小数</v>
+        <v>8263 ÷ 31 保留2位小数</v>
       </c>
       <c r="C269" t="str">
-        <v>❌ 渲染失败 [4607÷84(decimal)]: Upload failed (409): {"message":"is at b704da54021e0d8271f1fca50dd01211d1b4c87b but expected d91ad38b905322ea8a42f54a5b11cc9eec38636f","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254516314.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="270">
@@ -3368,10 +3368,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B270" t="str">
-        <v>9964 ÷ 16 保留3位小数</v>
+        <v>7748 ÷ 48 保留3位小数</v>
       </c>
       <c r="C270" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253240443.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254516423.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="271">
@@ -3379,10 +3379,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B271" t="str">
-        <v>4790 ÷ 90 保留4位小数</v>
+        <v>9169 ÷ 68 保留4位小数</v>
       </c>
       <c r="C271" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253240150.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254516224.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="272">
@@ -3390,10 +3390,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B272" t="str">
-        <v>160 ÷ 6.5 保留1位小数</v>
+        <v>104.8 ÷ 8.1 保留1位小数</v>
       </c>
       <c r="C272" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253241961.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254521068.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="273">
@@ -3401,10 +3401,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B273" t="str">
-        <v>750 ÷ 54 保留2位小数</v>
+        <v>4022 ÷ 26 保留2位小数</v>
       </c>
       <c r="C273" t="str">
-        <v>❌ 渲染失败 [750÷54(decimal)]: Upload failed (409): {"message":"is at fded58ada862f095cb5d92de80781d87a2401bd1 but expected 79c7d6ee7562c9797b6d89b8238f807e8ca6671c","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254520990.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="274">
@@ -3412,10 +3412,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B274" t="str">
-        <v>3115 ÷ 69 保留3位小数</v>
+        <v>4280 ÷ 44 保留3位小数</v>
       </c>
       <c r="C274" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253241714.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254520912.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="275">
@@ -3423,10 +3423,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B275" t="str">
-        <v>9157 ÷ 33 保留4位小数</v>
+        <v>7009 ÷ 82 保留4位小数</v>
       </c>
       <c r="C275" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253243574.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254525311.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="276">
@@ -3434,10 +3434,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B276" t="str">
-        <v>9847 ÷ 96 保留1位小数</v>
+        <v>7866 ÷ 70 保留1位小数</v>
       </c>
       <c r="C276" t="str">
-        <v>❌ 渲染失败 [9847÷96(decimal)]: Upload failed (409): {"message":"is at b1da8471b37534444844be4cbdf0c627c7239d1a but expected 432244838b20084304d45afff42b0e68f91d46d5","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254525207.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="277">
@@ -3445,10 +3445,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B277" t="str">
-        <v>910.5 ÷ 6.7 保留2位小数</v>
+        <v>790.5 ÷ 6.5 保留2位小数</v>
       </c>
       <c r="C277" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253243858.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254525510.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="278">
@@ -3456,10 +3456,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B278" t="str">
-        <v>1313 ÷ 44 保留3位小数</v>
+        <v>7343 ÷ 13 保留3位小数</v>
       </c>
       <c r="C278" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253245262.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254527832.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="279">
@@ -3467,10 +3467,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B279" t="str">
-        <v>4446 ÷ 5 保留4位小数</v>
+        <v>2133 ÷ 91 保留4位小数</v>
       </c>
       <c r="C279" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253244984.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254527683.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="280">
@@ -3478,10 +3478,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B280" t="str">
-        <v>206 ÷ 95 保留1位小数</v>
+        <v>5533 ÷ 97 保留1位小数</v>
       </c>
       <c r="C280" t="str">
-        <v>❌ 渲染失败 [206÷95(decimal)]: Upload failed (409): {"message":"is at 580baa17c8bd1a5236984e2e9c71875b45c5bcd1 but expected ed6ee30cecde487ea03bfb29fed7beacbe61ef42","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254527916.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="281">
@@ -3489,10 +3489,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B281" t="str">
-        <v>2553 ÷ 35 保留2位小数</v>
+        <v>6924 ÷ 59 保留2位小数</v>
       </c>
       <c r="C281" t="str">
-        <v>❌ 渲染失败 [2553÷35(decimal)]: Upload failed (409): {"message":"is at 7244b85d2724ebe4e24547b904ccd9828ac00a1c but expected b5935c9b9a436bfa9404468e876f16a732012141","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254533037.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="282">
@@ -3500,10 +3500,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B282" t="str">
-        <v>521.4 ÷ 0.7 保留3位小数</v>
+        <v>484 ÷ 2.9 保留3位小数</v>
       </c>
       <c r="C282" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253246464.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254532779.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="283">
@@ -3511,10 +3511,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B283" t="str">
-        <v>2548 ÷ 49 保留4位小数</v>
+        <v>9396 ÷ 63 保留4位小数</v>
       </c>
       <c r="C283" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253246773.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254532958.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="284">
@@ -3522,10 +3522,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B284" t="str">
-        <v>5762 ÷ 97 保留1位小数</v>
+        <v>2998 ÷ 46 保留1位小数</v>
       </c>
       <c r="C284" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253248546.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254537591.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="285">
@@ -3533,10 +3533,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B285" t="str">
-        <v>3930 ÷ 70 保留2位小数</v>
+        <v>111 ÷ 23 保留2位小数</v>
       </c>
       <c r="C285" t="str">
-        <v>❌ 渲染失败 [3930÷70(decimal)]: Upload failed (409): {"message":"is at 63d3094c9590ef1f02df744e846406a24a6c33b8 but expected 2f8692e5d1d2f35ef258fe41c42b3795215ef338","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254537393.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="286">
@@ -3544,10 +3544,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B286" t="str">
-        <v>454 ÷ 35 保留3位小数</v>
+        <v>9735 ÷ 84 保留3位小数</v>
       </c>
       <c r="C286" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253248294.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254538020.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="287">
@@ -3555,10 +3555,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B287" t="str">
-        <v>131.2 ÷ 2.2 保留4位小数</v>
+        <v>899 ÷ 5.4 保留4位小数</v>
       </c>
       <c r="C287" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253250270.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254540251.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="288">
@@ -3566,10 +3566,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B288" t="str">
-        <v>565 ÷ 53 保留1位小数</v>
+        <v>6619 ÷ 93 保留1位小数</v>
       </c>
       <c r="C288" t="str">
-        <v>❌ 渲染失败 [565÷53(decimal)]: Upload failed (409): {"message":"is at 56587611335f0daa5ca913613452fd7f82b1fddd but expected c73665a2f097a2615f54d9ca6c70d927d264e1bc","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254540463.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="289">
@@ -3577,10 +3577,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B289" t="str">
-        <v>2846 ÷ 36 保留2位小数</v>
+        <v>5586 ÷ 47 保留2位小数</v>
       </c>
       <c r="C289" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253249961.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254540164.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="290">
@@ -3588,10 +3588,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B290" t="str">
-        <v>8859 ÷ 68 保留3位小数</v>
+        <v>4350 ÷ 99 保留3位小数</v>
       </c>
       <c r="C290" t="str">
-        <v>❌ 渲染失败 [8859÷68(decimal)]: Upload failed (409): {"message":"is at 5b026ab2433f6d61a0a93df03199c357a754c293 but expected e62cc5fd963e05a78ef953ca0660d4929e41eac3","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254542793.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="291">
@@ -3599,10 +3599,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B291" t="str">
-        <v>7884 ÷ 39 保留4位小数</v>
+        <v>3592 ÷ 62 保留4位小数</v>
       </c>
       <c r="C291" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253251844.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254542938.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="292">
@@ -3610,10 +3610,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B292" t="str">
-        <v>191.8 ÷ 7.4 保留1位小数</v>
+        <v>303.3 ÷ 8.9 保留1位小数</v>
       </c>
       <c r="C292" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253251578.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254542479.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="293">
@@ -3621,10 +3621,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B293" t="str">
-        <v>6442 ÷ 65 保留2位小数</v>
+        <v>2158 ÷ 51 保留2位小数</v>
       </c>
       <c r="C293" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253253541.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254545405.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="294">
@@ -3632,10 +3632,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B294" t="str">
-        <v>4121 ÷ 6 保留3位小数</v>
+        <v>7900 ÷ 93 保留3位小数</v>
       </c>
       <c r="C294" t="str">
-        <v>❌ 渲染失败 [4121÷6(decimal)]: Upload failed (409): {"message":"is at 1bd82d16bf8a0924287299294d6a73aa7b8ccd68 but expected 341867c6be854c6838365f944a7d4d9e42aeb027","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254545319.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="295">
@@ -3643,10 +3643,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B295" t="str">
-        <v>4563 ÷ 52 保留4位小数</v>
+        <v>5543 ÷ 86 保留4位小数</v>
       </c>
       <c r="C295" t="str">
-        <v>❌ 渲染失败 [4563÷52(decimal)]: Upload failed (409): {"message":"is at 1bd82d16bf8a0924287299294d6a73aa7b8ccd68 but expected 341867c6be854c6838365f944a7d4d9e42aeb027","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254545242.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="296">
@@ -3654,10 +3654,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B296" t="str">
-        <v>1424 ÷ 7 保留1位小数</v>
+        <v>7599 ÷ 23 保留1位小数</v>
       </c>
       <c r="C296" t="str">
-        <v>❌ 渲染失败 [1424÷7(decimal)]: Upload failed (409): {"message":"is at bfab4f6b824b9ec5489b1b12853e21281e0791cb but expected 1bd82d16bf8a0924287299294d6a73aa7b8ccd68","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254549604.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="297">
@@ -3665,10 +3665,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B297" t="str">
-        <v>577.9 ÷ 7.9 保留2位小数</v>
+        <v>654.3 ÷ 2.2 保留2位小数</v>
       </c>
       <c r="C297" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253255060.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254549791.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="298">
@@ -3676,10 +3676,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B298" t="str">
-        <v>1245 ÷ 12 保留3位小数</v>
+        <v>886 ÷ 98 保留3位小数</v>
       </c>
       <c r="C298" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253255336.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254549713.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="299">
@@ -3687,10 +3687,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B299" t="str">
-        <v>8168 ÷ 95 保留4位小数</v>
+        <v>3653 ÷ 38 保留4位小数</v>
       </c>
       <c r="C299" t="str">
-        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776253256709.svg width=120px&gt;&lt;br&gt;</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254555025.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="300">
@@ -3698,10 +3698,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B300" t="str">
-        <v>1671 ÷ 43 保留1位小数</v>
+        <v>3870 ÷ 56 保留1位小数</v>
       </c>
       <c r="C300" t="str">
-        <v>❌ 渲染失败 [1671÷43(decimal)]: Upload failed (409): {"message":"is at e8eadc13439acc58b8899de4c9feebfb0816ffaf but expected 50510abb5c78fce52acc935fd8d253a957472001","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254554617.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="301">
@@ -3709,10 +3709,10 @@
         <v>render_division_decimal</v>
       </c>
       <c r="B301" t="str">
-        <v>6684 ÷ 49 保留2位小数</v>
+        <v>4143 ÷ 87 保留2位小数</v>
       </c>
       <c r="C301" t="str">
-        <v>❌ 渲染失败 [6684÷49(decimal)]: Upload failed (409): {"message":"is at e8eadc13439acc58b8899de4c9feebfb0816ffaf but expected 50510abb5c78fce52acc935fd8d253a957472001","documentation_url":"https://docs.github.com/rest/repos/contents#create-or-update-file</v>
+        <v>&lt;br&gt;&lt;img src=https://raw.githubusercontent.com/MIchael-wufan/test/main/images/vcalc_1776254554943.svg width=120px&gt;&lt;br&gt;</v>
       </c>
     </row>
   </sheetData>
